--- a/tools/importer/reports/import-knee-article.report.xlsx
+++ b/tools/importer/reports/import-knee-article.report.xlsx
@@ -61,7 +61,7 @@
     <t>knee-article</t>
   </si>
   <si>
-    <t>2026-07-18T18:08:19.170Z</t>
+    <t>2026-07-18T19:17:52.641Z</t>
   </si>
   <si>
     <t>10 Reasons to Call Your Doctor After Joint Replacement Surgery</t>
@@ -76,7 +76,7 @@
     <t>knee/30-items-to-pack-for-a-hospital-stay-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:08:33.495Z</t>
+    <t>2026-07-18T19:18:05.375Z</t>
   </si>
   <si>
     <t>30 Items to Pack for a Hospital Stay After Joint Replacement Surgery</t>
@@ -94,7 +94,7 @@
     <t>knee/4-common-joint-replacement-questions-and-answers</t>
   </si>
   <si>
-    <t>2026-07-18T17:49:15.125Z</t>
+    <t>2026-07-18T18:59:42.275Z</t>
   </si>
   <si>
     <t>4 Common Joint Replacement Questions &amp; Answers</t>
@@ -109,7 +109,7 @@
     <t>knee/4-reasons-why-people-participate-in-a-clinical-study</t>
   </si>
   <si>
-    <t>2026-07-18T18:16:38.503Z</t>
+    <t>2026-07-18T19:26:01.995Z</t>
   </si>
   <si>
     <t>4 Reasons why People Participate in a Clinical Study</t>
@@ -124,7 +124,7 @@
     <t>knee/5-ideas-to-keep-your-marriage-strong-while-managing-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:09:25.329Z</t>
+    <t>2026-07-18T19:18:53.744Z</t>
   </si>
   <si>
     <t>5 Ideas to Keep Your Marriage Strong While Managing Pain</t>
@@ -142,7 +142,7 @@
     <t>knee/5-signs-its-time-to-talk-to-your-doctor-about-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:20:09.181Z</t>
+    <t>2026-07-18T19:29:47.889Z</t>
   </si>
   <si>
     <t>5 Signs It’s Time to Talk to Your Doctor About Joint Replacement Surgery</t>
@@ -157,7 +157,7 @@
     <t>knee/5-ways-to-improve-sleep-when-you-have-chronic-pain</t>
   </si>
   <si>
-    <t>2026-07-18T17:57:34.776Z</t>
+    <t>2026-07-18T19:07:44.862Z</t>
   </si>
   <si>
     <t>Sleep Well With Chronic Pain | 5 Ways to Improve Sleep | ReadyPatient</t>
@@ -172,7 +172,7 @@
     <t>knee/6-different-items-to-pack-for-an-overnight-hospital-stay</t>
   </si>
   <si>
-    <t>2026-07-18T18:10:38.016Z</t>
+    <t>2026-07-18T19:19:52.680Z</t>
   </si>
   <si>
     <t>6 Different Items to Pack for an Overnight Hospital Stay</t>
@@ -190,7 +190,7 @@
     <t>knee/6-things-you-may-not-know-about-osteoarthritis</t>
   </si>
   <si>
-    <t>2026-07-18T18:03:38.815Z</t>
+    <t>2026-07-18T19:13:40.240Z</t>
   </si>
   <si>
     <t>6 Things You May Not Know About Osteoarthritis</t>
@@ -205,7 +205,7 @@
     <t>knee/6-ways-to-survive-the-holidays-with-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:07:46.853Z</t>
+    <t>2026-07-18T19:17:22.908Z</t>
   </si>
   <si>
     <t>6 Ways to Survive the Holidays with Joint Pain</t>
@@ -220,7 +220,7 @@
     <t>knee/7-things-to-look-for-in-a-remote-care-app</t>
   </si>
   <si>
-    <t>2026-07-18T17:58:45.055Z</t>
+    <t>2026-07-18T19:08:58.199Z</t>
   </si>
   <si>
     <t>7 Things to Look for in a Remote Care App</t>
@@ -235,7 +235,7 @@
     <t>knee/8-ways-to-stay-active-this-winter-with-arthritis</t>
   </si>
   <si>
-    <t>2026-07-18T18:10:10.286Z</t>
+    <t>2026-07-18T19:19:29.208Z</t>
   </si>
   <si>
     <t>8 Ways to Stay Active This Winter With Arthritis</t>
@@ -250,7 +250,7 @@
     <t>knee/9-fast-facts-about-arthritis</t>
   </si>
   <si>
-    <t>2026-07-18T17:57:47.856Z</t>
+    <t>2026-07-18T19:07:58.532Z</t>
   </si>
   <si>
     <t>9 Fast Facts About Arthritis</t>
@@ -268,7 +268,7 @@
     <t>knee/arthritic-painful-joints-motion-is-your-friend</t>
   </si>
   <si>
-    <t>2026-07-18T17:53:08.768Z</t>
+    <t>2026-07-18T19:03:19.822Z</t>
   </si>
   <si>
     <t>Arthritic, Painful Joints: Motion Is Your Friend</t>
@@ -286,7 +286,7 @@
     <t>knee/arthritis-age-is-there-an-appropriate-age-for-arthritic-pain</t>
   </si>
   <si>
-    <t>2026-07-18T17:50:08.482Z</t>
+    <t>2026-07-18T19:00:35.675Z</t>
   </si>
   <si>
     <t>Arthritis Age - Is There an Appropriate Age for Arthritic Pain?</t>
@@ -304,7 +304,7 @@
     <t>knee/arthritis-can-you-tell-the-facts-from-the-myths</t>
   </si>
   <si>
-    <t>2026-07-18T18:07:33.625Z</t>
+    <t>2026-07-18T19:17:10.202Z</t>
   </si>
   <si>
     <t>Arthritis – Can You Tell the Facts From the Myths?</t>
@@ -319,7 +319,7 @@
     <t>knee/attitude-and-outcome</t>
   </si>
   <si>
-    <t>2026-07-18T18:11:04.424Z</t>
+    <t>2026-07-18T19:20:17.996Z</t>
   </si>
   <si>
     <t>Attitude and Outcome</t>
@@ -334,7 +334,7 @@
     <t>knee/beckys-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T18:08:59.341Z</t>
+    <t>2026-07-18T19:18:30.327Z</t>
   </si>
   <si>
     <t>Becky's Patient Story – Knee Replacement</t>
@@ -349,7 +349,7 @@
     <t>knee/bills-bills-and-more-bills</t>
   </si>
   <si>
-    <t>2026-07-18T18:17:28.070Z</t>
+    <t>2026-07-18T19:26:56.547Z</t>
   </si>
   <si>
     <t>Bills, Bills… and More Bills!</t>
@@ -364,7 +364,7 @@
     <t>knee/bone-health-basics</t>
   </si>
   <si>
-    <t>2026-07-18T18:03:25.734Z</t>
+    <t>2026-07-18T19:13:27.479Z</t>
   </si>
   <si>
     <t>Bone Health Basics</t>
@@ -382,7 +382,7 @@
     <t>knee/brittani-simpson-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T17:53:49.612Z</t>
+    <t>2026-07-18T19:03:57.107Z</t>
   </si>
   <si>
     <t>Brittani Simpson Patient Story – Knee Replacement</t>
@@ -400,7 +400,7 @@
     <t>knee/building-strength-before-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:14:46.099Z</t>
+    <t>2026-07-18T19:24:03.610Z</t>
   </si>
   <si>
     <t>Building Strength Before Joint Replacement Surgery</t>
@@ -415,7 +415,7 @@
     <t>knee/can-i-go-without-narcotics-after-my-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:50:37.528Z</t>
+    <t>2026-07-18T19:01:01.283Z</t>
   </si>
   <si>
     <t>Can I Go Without Narcotics After My Surgery?</t>
@@ -430,7 +430,7 @@
     <t>knee/can-you-go-home-the-same-day-after-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T17:59:47.598Z</t>
+    <t>2026-07-18T19:09:56.867Z</t>
   </si>
   <si>
     <t>Can you go home the same day after knee replacement?</t>
@@ -445,7 +445,7 @@
     <t>knee/can-you-walk-right-after-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:56:56.768Z</t>
+    <t>2026-07-18T19:07:10.615Z</t>
   </si>
   <si>
     <t>Can You Walk Right After Knee Replacement Surgery?</t>
@@ -463,7 +463,7 @@
     <t>knee/caring-for-a-loved-one-after-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:20:48.808Z</t>
+    <t>2026-07-18T19:30:29.477Z</t>
   </si>
   <si>
     <t>Caring for a Loved One After Surgery</t>
@@ -478,7 +478,7 @@
     <t>knee/common-post-op-questions-and-answers</t>
   </si>
   <si>
-    <t>2026-07-18T18:20:23.361Z</t>
+    <t>2026-07-18T19:30:02.729Z</t>
   </si>
   <si>
     <t>Common Post-Op Questions and Answers</t>
@@ -493,7 +493,7 @@
     <t>knee/common-recovery-exercises-after-hip-and-knee-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T18:14:34.455Z</t>
+    <t>2026-07-18T19:23:49.407Z</t>
   </si>
   <si>
     <t>Common recovery exercises after hip and knee replacements</t>
@@ -511,7 +511,7 @@
     <t>knee/common-side-effects-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:19:13.735Z</t>
+    <t>2026-07-18T19:28:47.045Z</t>
   </si>
   <si>
     <t>Common Side Effects After Joint Replacement Surgery | ReadyPatient</t>
@@ -529,7 +529,7 @@
     <t>knee/connies-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T17:54:37.674Z</t>
+    <t>2026-07-18T19:04:48.276Z</t>
   </si>
   <si>
     <t>Connie's Patient Story - Double Knee Replacement</t>
@@ -544,7 +544,7 @@
     <t>knee/consecutive-knee-or-hip-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T18:00:51.329Z</t>
+    <t>2026-07-18T19:10:55.304Z</t>
   </si>
   <si>
     <t>Consecutive Knee or Hip Replacements</t>
@@ -559,7 +559,7 @@
     <t>knee/considering-joint-surgery-while-living-alone</t>
   </si>
   <si>
-    <t>2026-07-18T18:12:51.525Z</t>
+    <t>2026-07-18T19:22:04.148Z</t>
   </si>
   <si>
     <t>Considering Joint Surgery While Living Alone</t>
@@ -574,7 +574,7 @@
     <t>knee/considering-joint-surgery-while-raising-a-family</t>
   </si>
   <si>
-    <t>2026-07-18T18:17:14.293Z</t>
+    <t>2026-07-18T19:26:42.251Z</t>
   </si>
   <si>
     <t>Considering Joint Surgery While Raising a Family</t>
@@ -589,7 +589,7 @@
     <t>knee/covid-19-has-delayed-my-joint-surgery-but-i-still-hurt</t>
   </si>
   <si>
-    <t>2026-07-18T18:01:31.296Z</t>
+    <t>2026-07-18T19:11:37.974Z</t>
   </si>
   <si>
     <t>COVID-19 Has Delayed My Joint Surgery, but I Still Hurt…</t>
@@ -604,7 +604,7 @@
     <t>knee/decoding-insurance-coding</t>
   </si>
   <si>
-    <t>2026-07-18T18:15:45.117Z</t>
+    <t>2026-07-18T19:25:06.523Z</t>
   </si>
   <si>
     <t>Decoding Insurance Coding</t>
@@ -619,7 +619,7 @@
     <t>knee/defining-your-personal-success</t>
   </si>
   <si>
-    <t>2026-07-18T18:12:00.331Z</t>
+    <t>2026-07-18T19:21:08.099Z</t>
   </si>
   <si>
     <t>Defining Your Personal Success</t>
@@ -637,7 +637,7 @@
     <t>knee/denise-good-partial-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T17:49:28.026Z</t>
+    <t>2026-07-18T18:59:54.178Z</t>
   </si>
   <si>
     <t>Denise's Patient Story - Partial Knee Replacement</t>
@@ -655,7 +655,7 @@
     <t>knee/diagnostic-imaging-tools-used-to-evaluate-your-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T17:51:45.457Z</t>
+    <t>2026-07-18T19:02:04.248Z</t>
   </si>
   <si>
     <t>Diagnostic Imaging Tools Used to Evaluate Your Joint Pain</t>
@@ -670,7 +670,7 @@
     <t>knee/do-i-have-bowlegs-or-knock-knees</t>
   </si>
   <si>
-    <t>2026-07-18T18:10:23.323Z</t>
+    <t>2026-07-18T19:19:40.265Z</t>
   </si>
   <si>
     <t>Do I Have Bowlegs or Knock Knees?</t>
@@ -685,7 +685,7 @@
     <t>knee/do-i-really-need-physical-therapy-after-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:51:58.827Z</t>
+    <t>2026-07-18T19:02:16.861Z</t>
   </si>
   <si>
     <t>Do I Really Need Physical Therapy After Surgery (Or Sometimes Even Before)?</t>
@@ -700,7 +700,7 @@
     <t>knee/do-you-stay-overnight-after-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:01:43.192Z</t>
+    <t>2026-07-18T19:11:50.364Z</t>
   </si>
   <si>
     <t>Does Knee Replacement Surgery Require an Overnight Stay? | ReadyPatient</t>
@@ -715,7 +715,7 @@
     <t>knee/donalds-patient-story-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:11:46.070Z</t>
+    <t>2026-07-18T19:20:55.550Z</t>
   </si>
   <si>
     <t>Donald's Patient Story – Knee Replacement</t>
@@ -733,7 +733,7 @@
     <t>knee/exercises-for-knee-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:19:42.206Z</t>
+    <t>2026-07-18T19:29:17.604Z</t>
   </si>
   <si>
     <t>Exercises for Knee Pain | ReadyPatient</t>
@@ -748,7 +748,7 @@
     <t>knee/fatigue-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:19:29.127Z</t>
+    <t>2026-07-18T19:29:01.479Z</t>
   </si>
   <si>
     <t>Fatigue after Joint Replacement Surgery | ReadyPatient</t>
@@ -766,7 +766,7 @@
     <t>knee/financial-considerations-for-the-younger-joint-replacement-patient</t>
   </si>
   <si>
-    <t>2026-07-18T17:51:17.431Z</t>
+    <t>2026-07-18T19:01:38.378Z</t>
   </si>
   <si>
     <t>Financial Considerations for the Younger Joint Replacement Patient</t>
@@ -781,7 +781,7 @@
     <t>knee/financial-planning-for-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:05:54.225Z</t>
+    <t>2026-07-18T19:15:46.141Z</t>
   </si>
   <si>
     <t>Financial Planning for Joint Replacement Surgery</t>
@@ -796,7 +796,7 @@
     <t>knee/five-things-to-consider-when-selecting-an-orthopedic-surgeon</t>
   </si>
   <si>
-    <t>2026-07-18T18:21:02.242Z</t>
+    <t>2026-07-18T19:30:43.278Z</t>
   </si>
   <si>
     <t>5 Things to Consider When Choosing an Orthopedic Surgeon</t>
@@ -811,7 +811,7 @@
     <t>knee/flying-and-medical-implants-etiquette-for-going-through-security</t>
   </si>
   <si>
-    <t>2026-07-18T18:21:16.163Z</t>
+    <t>2026-07-18T19:30:56.069Z</t>
   </si>
   <si>
     <t>Flying with a Medical Implant or Prosthetic Device | ReadyPatient</t>
@@ -826,7 +826,7 @@
     <t>knee/gardening-with-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:12:12.476Z</t>
+    <t>2026-07-18T19:21:21.879Z</t>
   </si>
   <si>
     <t>Gardening with Joint Pain</t>
@@ -841,7 +841,7 @@
     <t>knee/garys-patient-story-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:15:58.107Z</t>
+    <t>2026-07-18T19:25:19.475Z</t>
   </si>
   <si>
     <t>Gary's Patient Story – Knee Replacement</t>
@@ -856,7 +856,7 @@
     <t>knee/getting-a-second-opinion</t>
   </si>
   <si>
-    <t>2026-07-18T18:15:05.289Z</t>
+    <t>2026-07-18T19:24:24.340Z</t>
   </si>
   <si>
     <t>Getting a Second Opinion</t>
@@ -871,7 +871,7 @@
     <t>knee/handling-insurance-appeals</t>
   </si>
   <si>
-    <t>2026-07-18T18:17:56.350Z</t>
+    <t>2026-07-18T19:27:23.202Z</t>
   </si>
   <si>
     <t>Handling Insurance Appeals</t>
@@ -886,7 +886,7 @@
     <t>knee/having-fun-this-summer-despite-your-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:12:26.157Z</t>
+    <t>2026-07-18T19:21:35.987Z</t>
   </si>
   <si>
     <t>Having Fun this Summer Despite Your Joint Pain</t>
@@ -904,7 +904,7 @@
     <t>knee/hip-and-knee-replacement-cementless-vs-cemented-implants</t>
   </si>
   <si>
-    <t>2026-07-18T17:52:55.490Z</t>
+    <t>2026-07-18T19:03:06.706Z</t>
   </si>
   <si>
     <t>Hip and Knee Replacement: Cementless vs Cemented Implants</t>
@@ -919,7 +919,7 @@
     <t>knee/how-do-i-take-care-of-my-new-joint-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:06:40.623Z</t>
+    <t>2026-07-18T19:16:22.117Z</t>
   </si>
   <si>
     <t>How Do I Take Care of My New Joint Replacement?</t>
@@ -934,7 +934,7 @@
     <t>knee/how-long-will-it-take-to-get-back-to-normal-after-joint-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:55:30.798Z</t>
+    <t>2026-07-18T19:05:44.877Z</t>
   </si>
   <si>
     <t>How Long Will It Take To Get Back to Normal After Joint Surgery?</t>
@@ -949,7 +949,7 @@
     <t>knee/how-tech-savvy-are-you</t>
   </si>
   <si>
-    <t>2026-07-18T18:18:10.711Z</t>
+    <t>2026-07-18T19:27:37.442Z</t>
   </si>
   <si>
     <t>How tech-savvy are you?</t>
@@ -964,7 +964,7 @@
     <t>knee/how-to-prepare-for-revision-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:11:17.266Z</t>
+    <t>2026-07-18T19:20:30.391Z</t>
   </si>
   <si>
     <t>How to Prepare for Revision Surgery</t>
@@ -979,7 +979,7 @@
     <t>knee/incision-care-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:09:55.895Z</t>
+    <t>2026-07-18T19:19:17.019Z</t>
   </si>
   <si>
     <t>Incision Care After Joint Replacement Surgery</t>
@@ -994,7 +994,7 @@
     <t>knee/infection-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:55:01.344Z</t>
+    <t>2026-07-18T19:05:13.536Z</t>
   </si>
   <si>
     <t>Infection After Joint Replacement Surgery</t>
@@ -1009,7 +1009,7 @@
     <t>knee/insurance-and-joint-replacement-your-guide-to-getting-started</t>
   </si>
   <si>
-    <t>2026-07-18T18:04:57.652Z</t>
+    <t>2026-07-18T19:14:56.428Z</t>
   </si>
   <si>
     <t>Insurance and Joint Replacement - Your Guide to Getting Started</t>
@@ -1024,7 +1024,7 @@
     <t>knee/insurance-related-questions-to-ask</t>
   </si>
   <si>
-    <t>2026-07-18T18:15:33.077Z</t>
+    <t>2026-07-18T19:24:52.280Z</t>
   </si>
   <si>
     <t>Insurance Related Questions to Ask</t>
@@ -1039,7 +1039,7 @@
     <t>knee/is-arthritis-a-normal-part-of-aging</t>
   </si>
   <si>
-    <t>2026-07-18T17:51:04.173Z</t>
+    <t>2026-07-18T19:01:26.305Z</t>
   </si>
   <si>
     <t>Is Arthritis a Normal Part of Aging?</t>
@@ -1054,7 +1054,7 @@
     <t>knee/jims-patient-story-double-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:19:55.275Z</t>
+    <t>2026-07-18T19:29:31.317Z</t>
   </si>
   <si>
     <t>Jim’s Patient Story – Double Knee Replacement | ReadyPatient</t>
@@ -1069,7 +1069,7 @@
     <t>knee/joint-replacement-during-covid-questions-to-ask-your-doctor</t>
   </si>
   <si>
-    <t>2026-07-18T17:59:36.074Z</t>
+    <t>2026-07-18T19:09:44.482Z</t>
   </si>
   <si>
     <t>Joint Replacement During the COVID-19 Pandemic - Questions to Ask Your Doctor</t>
@@ -1084,7 +1084,7 @@
     <t>knee/joint-replacement-myth-1-surgical-robots-perform-the-whole-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:51:31.961Z</t>
+    <t>2026-07-18T19:01:51.315Z</t>
   </si>
   <si>
     <t>Joint Replacement Myth #1: Surgical Robots Perform the Whole Surgery</t>
@@ -1099,7 +1099,7 @@
     <t>knee/joint-replacement-myth-2-partial-knee-replacement-leads-to-total</t>
   </si>
   <si>
-    <t>2026-07-18T17:48:59.605Z</t>
+    <t>2026-07-18T18:59:28.705Z</t>
   </si>
   <si>
     <t>Joint Replacement Myth #2: Partial Knee Replacement Leads to Total</t>
@@ -1114,7 +1114,7 @@
     <t>knee/joint-replacement-myth-3-about-knee-injections</t>
   </si>
   <si>
-    <t>2026-07-18T17:54:14.638Z</t>
+    <t>2026-07-18T19:04:23.042Z</t>
   </si>
   <si>
     <t>Joint Replacement Myth #3: About Knee Injections</t>
@@ -1129,7 +1129,7 @@
     <t>knee/joint-replacement-surgery-during-the-covid-19-pandemic</t>
   </si>
   <si>
-    <t>2026-07-18T17:54:26.135Z</t>
+    <t>2026-07-18T19:04:35.853Z</t>
   </si>
   <si>
     <t>Joint Replacement Surgery During the COVID-19 Pandemic</t>
@@ -1147,7 +1147,7 @@
     <t>knee/keloid-and-hypertrophic-scars</t>
   </si>
   <si>
-    <t>2026-07-18T17:50:22.395Z</t>
+    <t>2026-07-18T19:00:47.491Z</t>
   </si>
   <si>
     <t>Keloid and Hypertrophic Scars</t>
@@ -1165,7 +1165,7 @@
     <t>knee/knee-implant-size-and-shape-do-they-matter</t>
   </si>
   <si>
-    <t>2026-07-18T17:49:55.060Z</t>
+    <t>2026-07-18T19:00:20.373Z</t>
   </si>
   <si>
     <t>Knee Implant Size and Shape – Do They Matter?</t>
@@ -1216,7 +1216,7 @@
     <t>knee/knee-pain-explained</t>
   </si>
   <si>
-    <t>2026-07-17T16:42:15.863Z</t>
+    <t>2026-07-18T18:58:21.225Z</t>
   </si>
   <si>
     <t>Knee Pain Explained</t>
@@ -1228,7 +1228,7 @@
     <t>knee/knee-pain-relief-nonsurgical-treatment-options</t>
   </si>
   <si>
-    <t>2026-07-18T18:05:26.325Z</t>
+    <t>2026-07-18T19:15:20.171Z</t>
   </si>
   <si>
     <t>Knee Pain Relief &amp; Treatment - Nonsurigcal Treatment Options | ReadyPatient</t>
@@ -1243,7 +1243,7 @@
     <t>knee/knee-pain-relief-surgical-treatment-options</t>
   </si>
   <si>
-    <t>2026-07-18T18:02:58.616Z</t>
+    <t>2026-07-18T19:13:02.551Z</t>
   </si>
   <si>
     <t>Knee Pain Relief &amp; Surgical Treatment Options | ReadyPatient</t>
@@ -1258,7 +1258,7 @@
     <t>knee/know-your-procedure-options-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:11:30.759Z</t>
+    <t>2026-07-18T19:20:42.689Z</t>
   </si>
   <si>
     <t>Know Your Procedure Options – Knee Replacement</t>
@@ -1273,7 +1273,7 @@
     <t>knee/limitations-of-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:13:03.030Z</t>
+    <t>2026-07-18T19:22:17.678Z</t>
   </si>
   <si>
     <t>Limitations of Knee Replacement Surgery | ReadyPatient</t>
@@ -1288,7 +1288,7 @@
     <t>knee/lost-your-job-and-insurance-because-of-covid-19-but-need-joint-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:59:10.314Z</t>
+    <t>2026-07-18T19:09:21.182Z</t>
   </si>
   <si>
     <t>Lost Your Job Because of COVID-19</t>
@@ -1303,7 +1303,7 @@
     <t>knee/maintaining-joint-health</t>
   </si>
   <si>
-    <t>2026-07-18T18:16:51.114Z</t>
+    <t>2026-07-18T19:26:14.976Z</t>
   </si>
   <si>
     <t>Maintaining Joint Health</t>
@@ -1318,7 +1318,7 @@
     <t>knee/managing-a-loved-ones-postsurgical-care-during-covid-19</t>
   </si>
   <si>
-    <t>2026-07-18T18:01:55.946Z</t>
+    <t>2026-07-18T19:12:02.423Z</t>
   </si>
   <si>
     <t>Managing a Loved One’s Postsurgical Care During COVID-19</t>
@@ -1333,7 +1333,7 @@
     <t>knee/managing-constipation-after-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:57:08.926Z</t>
+    <t>2026-07-18T19:07:20.997Z</t>
   </si>
   <si>
     <t>Managing Constipation After Surgery</t>
@@ -1348,7 +1348,7 @@
     <t>knee/managing-your-stress-while-caring-for-another</t>
   </si>
   <si>
-    <t>2026-07-18T18:03:52.054Z</t>
+    <t>2026-07-18T19:13:52.533Z</t>
   </si>
   <si>
     <t>Managing Your Stress While Caring for Another</t>
@@ -1363,7 +1363,7 @@
     <t>knee/medical-tourniquets</t>
   </si>
   <si>
-    <t>2026-07-18T18:19:03.886Z</t>
+    <t>2026-07-18T19:28:31.490Z</t>
   </si>
   <si>
     <t>Medical Tourniquets | Tourniquets used during surgery | ReadyPatient</t>
@@ -1378,7 +1378,7 @@
     <t>knee/metal-hypersensitivity-and-allergies</t>
   </si>
   <si>
-    <t>2026-07-18T17:52:26.515Z</t>
+    <t>2026-07-18T19:02:41.795Z</t>
   </si>
   <si>
     <t>Metal Hypersensitivity and Allergies</t>
@@ -1393,7 +1393,7 @@
     <t>knee/moving-with-morning-joint-stiffness</t>
   </si>
   <si>
-    <t>2026-07-18T18:04:31.895Z</t>
+    <t>2026-07-18T19:14:31.430Z</t>
   </si>
   <si>
     <t>Moving with Morning Joint Stiffness</t>
@@ -1408,7 +1408,7 @@
     <t>knee/nancy-lopez-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T18:15:19.307Z</t>
+    <t>2026-07-18T19:24:39.973Z</t>
   </si>
   <si>
     <t>Nancy Lopez Patient Story – Knee Replacement</t>
@@ -1423,7 +1423,7 @@
     <t>knee/nicotine-and-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:56:45.110Z</t>
+    <t>2026-07-18T19:06:59.146Z</t>
   </si>
   <si>
     <t>Nicotine and Surgery</t>
@@ -1438,7 +1438,7 @@
     <t>knee/no-food-or-drink-after-midnight</t>
   </si>
   <si>
-    <t>2026-07-18T17:56:33.329Z</t>
+    <t>2026-07-18T19:06:46.391Z</t>
   </si>
   <si>
     <t>No Food or Drink After Midnight?</t>
@@ -1453,7 +1453,7 @@
     <t>knee/on-bended-knee-peters-patient-story-video</t>
   </si>
   <si>
-    <t>2026-07-18T18:04:18.561Z</t>
+    <t>2026-07-18T19:14:17.634Z</t>
   </si>
   <si>
     <t>Peter's Patient Story – Partial Knee Replacement</t>
@@ -1471,7 +1471,7 @@
     <t>knee/orthopedic-implants-and-metal-sensitivity</t>
   </si>
   <si>
-    <t>2026-07-18T18:13:29.346Z</t>
+    <t>2026-07-18T19:22:43.479Z</t>
   </si>
   <si>
     <t>Orthopedic Implants and Metal Sensitivity | ReadyPatient</t>
@@ -1486,7 +1486,7 @@
     <t>knee/outpatient-joint-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T17:55:43.136Z</t>
+    <t>2026-07-18T19:05:57.059Z</t>
   </si>
   <si>
     <t>Outpatient Joint Replacement</t>
@@ -1521,7 +1521,7 @@
     <t>knee/pain-isnt-weakness</t>
   </si>
   <si>
-    <t>2026-07-18T17:49:41.508Z</t>
+    <t>2026-07-18T19:00:06.539Z</t>
   </si>
   <si>
     <t>Pain Isn't "Weakness"</t>
@@ -1536,7 +1536,7 @@
     <t>knee/patricks-patient-story-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T17:53:37.092Z</t>
+    <t>2026-07-18T19:03:46.027Z</t>
   </si>
   <si>
     <t>Patrick's Patient Story – Knee Replacement</t>
@@ -1551,7 +1551,7 @@
     <t>knee/physical-therapy-options-in-the-covid-era</t>
   </si>
   <si>
-    <t>2026-07-18T17:50:50.521Z</t>
+    <t>2026-07-18T19:01:14.070Z</t>
   </si>
   <si>
     <t>Physical Therapy Options in the COVID Era</t>
@@ -1566,7 +1566,7 @@
     <t>knee/post-op-pain-management-strategies-for-orthopedic-patients</t>
   </si>
   <si>
-    <t>2026-07-18T18:02:45.894Z</t>
+    <t>2026-07-18T19:12:50.524Z</t>
   </si>
   <si>
     <t>Post-Op Pain Management Strategies for Orthopedic Patients</t>
@@ -1581,7 +1581,7 @@
     <t>knee/pre-op-and-post-op-joint-replacement-appointments-are-they-necessary</t>
   </si>
   <si>
-    <t>2026-07-18T17:58:09.586Z</t>
+    <t>2026-07-18T19:08:22.694Z</t>
   </si>
   <si>
     <t>Pre-op and Post-op Joint Replacement Appointments – Are They Necessary?</t>
@@ -1596,7 +1596,7 @@
     <t>knee/prepare-for-hip-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:56:07.887Z</t>
+    <t>2026-07-18T19:06:21.781Z</t>
   </si>
   <si>
     <t>Prepare for Ankle, Hip, Knee Replacement or Foot Surgery</t>
@@ -1614,7 +1614,7 @@
     <t>knee/preparing-for-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:05:39.593Z</t>
+    <t>2026-07-18T19:15:32.328Z</t>
   </si>
   <si>
     <t>Preparing for Joint Replacement Surgery</t>
@@ -1629,7 +1629,7 @@
     <t>knee/preparing-for-surgery-when-you-cant-have-visitors</t>
   </si>
   <si>
-    <t>2026-07-18T17:58:57.780Z</t>
+    <t>2026-07-18T19:09:09.320Z</t>
   </si>
   <si>
     <t>Preparing for Surgery When You Can’t Have Visitors</t>
@@ -1644,7 +1644,7 @@
     <t>knee/questions-to-ask-when-considering-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:06:54.336Z</t>
+    <t>2026-07-18T19:16:33.192Z</t>
   </si>
   <si>
     <t>Questions to Ask When Considering Knee Replacement Surgery</t>
@@ -1662,7 +1662,7 @@
     <t>knee/rachaels-knee-replacement-surgery-story</t>
   </si>
   <si>
-    <t>2026-07-18T18:18:38.001Z</t>
+    <t>2026-07-18T19:28:05.343Z</t>
   </si>
   <si>
     <t>Rachael’s Knee Replacement Surgery Story | ReadyPatient</t>
@@ -1677,7 +1677,7 @@
     <t>knee/rebeccas-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T17:52:41.179Z</t>
+    <t>2026-07-18T19:02:54.494Z</t>
   </si>
   <si>
     <t>Rebecca's Patient Story – Knee Replacement</t>
@@ -1692,7 +1692,7 @@
     <t>knee/recovering-from-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:08:00.746Z</t>
+    <t>2026-07-18T19:17:35.540Z</t>
   </si>
   <si>
     <t>Recovering from Joint Replacement Surgery</t>
@@ -1707,7 +1707,7 @@
     <t>knee/referred-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:12:38.189Z</t>
+    <t>2026-07-18T19:21:49.773Z</t>
   </si>
   <si>
     <t>Referred Pain</t>
@@ -1722,7 +1722,7 @@
     <t>knee/resources-for-caregivers-caring-for-someone-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:18:25.063Z</t>
+    <t>2026-07-18T19:27:52.694Z</t>
   </si>
   <si>
     <t>Resources for Caregivers: Caring for Someone After Joint Replacement Surgery</t>
@@ -1737,7 +1737,7 @@
     <t>knee/returning-home-after-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:05:10.457Z</t>
+    <t>2026-07-18T19:15:08.286Z</t>
   </si>
   <si>
     <t>Returning Home After Knee Replacement Surgery</t>
@@ -1752,7 +1752,7 @@
     <t>knee/returning-to-activity-after-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:03:12.034Z</t>
+    <t>2026-07-18T19:13:13.916Z</t>
   </si>
   <si>
     <t>Returning to Activity After Knee Replacement Surgery</t>
@@ -1767,7 +1767,7 @@
     <t>knee/returning-to-activity-after-total-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:13:43.155Z</t>
+    <t>2026-07-18T19:22:56.774Z</t>
   </si>
   <si>
     <t>Returning to Activity After Total Knee Replacement | ReadyPatient</t>
@@ -1782,7 +1782,7 @@
     <t>knee/revision-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:55:55.478Z</t>
+    <t>2026-07-18T19:06:08.872Z</t>
   </si>
   <si>
     <t>Revision Joint Replacement Surgery</t>
@@ -1797,7 +1797,7 @@
     <t>knee/roberts-patient-story-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T17:48:32.593Z</t>
+    <t>2026-07-18T18:59:04.947Z</t>
   </si>
   <si>
     <t>Robert's Patient Story – Knee Replacement</t>
@@ -1812,7 +1812,7 @@
     <t>knee/robots-doing-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:10:49.796Z</t>
+    <t>2026-07-18T19:20:05.423Z</t>
   </si>
   <si>
     <t>Robots Doing Surgery?</t>
@@ -1827,7 +1827,7 @@
     <t>knee/robots-used-in-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:48:44.601Z</t>
+    <t>2026-07-18T18:59:17.164Z</t>
   </si>
   <si>
     <t>Robots Used in Surgery</t>
@@ -1842,7 +1842,7 @@
     <t>knee/scheduling-your-surgery-after-the-covid-19-quarantine</t>
   </si>
   <si>
-    <t>2026-07-18T17:56:21.224Z</t>
+    <t>2026-07-18T19:06:33.149Z</t>
   </si>
   <si>
     <t>Scheduling Your Surgery After the COVID-19 Quarantine</t>
@@ -1857,7 +1857,7 @@
     <t>knee/self-quarantine-before-and-after-your-elective-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:01:03.853Z</t>
+    <t>2026-07-18T19:11:07.812Z</t>
   </si>
   <si>
     <t>Self-Quarantine Before (and After) Your Elective Surgery</t>
@@ -1872,7 +1872,7 @@
     <t>knee/setting-realistic-expectations-prior-to-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:04:45.390Z</t>
+    <t>2026-07-18T19:14:43.994Z</t>
   </si>
   <si>
     <t>Setting Realistic Expectations Prior to Joint Replacement Surgery</t>
@@ -1887,7 +1887,7 @@
     <t>knee/shots-and-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:09:11.824Z</t>
+    <t>2026-07-18T19:18:41.792Z</t>
   </si>
   <si>
     <t>Shots and Joint Pain</t>
@@ -1902,7 +1902,7 @@
     <t>knee/so-your-doctor-said-you-need-joint-replacement-surgery-whats-next</t>
   </si>
   <si>
-    <t>2026-07-18T18:09:40.505Z</t>
+    <t>2026-07-18T19:19:04.707Z</t>
   </si>
   <si>
     <t>So Your Doctor Said You Need Joint Replacement Surgery… What’s Next?</t>
@@ -1917,7 +1917,7 @@
     <t>knee/social-distancing-and-joint-pain-a-few-things-to-consider</t>
   </si>
   <si>
-    <t>2026-07-18T17:57:21.750Z</t>
+    <t>2026-07-18T19:07:33.927Z</t>
   </si>
   <si>
     <t>Social Distancing and Joint Pain – A Few Things to Consider</t>
@@ -1932,7 +1932,7 @@
     <t>knee/spring-cleaning-with-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:08:46.103Z</t>
+    <t>2026-07-18T19:18:17.906Z</t>
   </si>
   <si>
     <t>Spring Cleaning With Joint Pain</t>
@@ -1947,7 +1947,7 @@
     <t>knee/superfoods-for-joint-health</t>
   </si>
   <si>
-    <t>2026-07-18T18:07:08.736Z</t>
+    <t>2026-07-18T19:16:44.793Z</t>
   </si>
   <si>
     <t>Superfoods for Joint Health</t>
@@ -1962,7 +1962,7 @@
     <t>knee/surgery-during-covid-19-what-are-hospitals-doing-to-manage-my-safety</t>
   </si>
   <si>
-    <t>2026-07-18T17:57:58.487Z</t>
+    <t>2026-07-18T19:08:10.204Z</t>
   </si>
   <si>
     <t>Surgery During COVID-19: What are Hospitals Doing to Manage My Safety?</t>
@@ -1977,7 +1977,7 @@
     <t>knee/surgical-principles-and-goals-for-total-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:14:21.876Z</t>
+    <t>2026-07-18T19:23:36.296Z</t>
   </si>
   <si>
     <t>Surgical Principles and Goals for Total Knee Replacement | ReadyPatient</t>
@@ -1992,7 +1992,7 @@
     <t>knee/swimming-a-great-exercise-for-every-age-and-fitness-level</t>
   </si>
   <si>
-    <t>2026-07-18T18:02:20.229Z</t>
+    <t>2026-07-18T19:12:26.385Z</t>
   </si>
   <si>
     <t>Swimming: A Great Exercise for Every Age and Fitness Level</t>
@@ -2007,7 +2007,7 @@
     <t>knee/technology-and-the-telehealth-landscape</t>
   </si>
   <si>
-    <t>2026-07-18T18:00:24.479Z</t>
+    <t>2026-07-18T19:10:32.516Z</t>
   </si>
   <si>
     <t>Technology and the Telehealth Landscape</t>
@@ -2022,7 +2022,7 @@
     <t>knee/telehealth-and-remote-care-evolving-in-the-age-of-covid-19</t>
   </si>
   <si>
-    <t>2026-07-18T18:02:08.797Z</t>
+    <t>2026-07-18T19:12:15.343Z</t>
   </si>
   <si>
     <t>Telehealth and Remote Care - Evolving in the Age of COVID-19</t>
@@ -2037,7 +2037,7 @@
     <t>knee/the-basics-of-using-a-walking-aid</t>
   </si>
   <si>
-    <t>2026-07-18T17:52:12.295Z</t>
+    <t>2026-07-18T19:02:29.811Z</t>
   </si>
   <si>
     <t>The Basics of Using a Walking Aid</t>
@@ -2052,7 +2052,7 @@
     <t>knee/the-benefits-of-outpatient-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T17:58:33.471Z</t>
+    <t>2026-07-18T19:08:46.866Z</t>
   </si>
   <si>
     <t>The Benefits of Outpatient Joint Replacement Surgery</t>
@@ -2067,7 +2067,7 @@
     <t>knee/the-effect-of-excess-weight-on-your-joints</t>
   </si>
   <si>
-    <t>2026-07-18T18:21:28.271Z</t>
+    <t>2026-07-18T19:31:11.519Z</t>
   </si>
   <si>
     <t>The Effect of Excess Weight on Your Joints</t>
@@ -2082,7 +2082,7 @@
     <t>knee/the-effect-of-joint-pain-on-you-and-your-family</t>
   </si>
   <si>
-    <t>2026-07-18T18:16:11.948Z</t>
+    <t>2026-07-18T19:25:34.089Z</t>
   </si>
   <si>
     <t>The Effect of Joint Pain on You and Your Family</t>
@@ -2097,7 +2097,7 @@
     <t>knee/the-pain-paradox</t>
   </si>
   <si>
-    <t>2026-07-18T17:54:01.911Z</t>
+    <t>2026-07-18T19:04:09.674Z</t>
   </si>
   <si>
     <t>The Pain Paradox</t>
@@ -2112,7 +2112,7 @@
     <t>knee/the-relationship-between-joint-pain-and-food</t>
   </si>
   <si>
-    <t>2026-07-18T17:58:21.728Z</t>
+    <t>2026-07-18T19:08:33.936Z</t>
   </si>
   <si>
     <t>The Relationship Between Joint Pain and Food</t>
@@ -2127,7 +2127,7 @@
     <t>knee/the-return-of-elective-procedures-explained</t>
   </si>
   <si>
-    <t>2026-07-18T18:00:37.847Z</t>
+    <t>2026-07-18T19:10:44.634Z</t>
   </si>
   <si>
     <t>The Return of Elective Procedures Explained</t>
@@ -2142,7 +2142,7 @@
     <t>knee/things-to-do-during-an-overnight-hospital-stay</t>
   </si>
   <si>
-    <t>2026-07-18T18:00:13.444Z</t>
+    <t>2026-07-18T19:10:21.465Z</t>
   </si>
   <si>
     <t>Things to Do During an Overnight Hospital Stay</t>
@@ -2157,7 +2157,7 @@
     <t>knee/types-of-joint-injections</t>
   </si>
   <si>
-    <t>2026-07-18T17:55:18.421Z</t>
+    <t>2026-07-18T19:05:32.683Z</t>
   </si>
   <si>
     <t>Types of Joint Injections</t>
@@ -2172,7 +2172,7 @@
     <t>knee/understanding-your-loved-ones-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:07:21.338Z</t>
+    <t>2026-07-18T19:16:56.660Z</t>
   </si>
   <si>
     <t>Understanding Your Loved One’s Joint Pain</t>
@@ -2187,7 +2187,7 @@
     <t>knee/what-are-the-risks-of-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:20:35.258Z</t>
+    <t>2026-07-18T19:30:15.588Z</t>
   </si>
   <si>
     <t>What Are the Risks of Knee Replacement Surgery?</t>
@@ -2202,7 +2202,7 @@
     <t>knee/what-happens-during-partial-knee-and-total-knee-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T18:13:56.369Z</t>
+    <t>2026-07-18T19:23:10.852Z</t>
   </si>
   <si>
     <t>What Happens During Partial Knee and Total Knee Replacements | ReadyPatient</t>
@@ -2220,7 +2220,7 @@
     <t>knee/what-happens-during-partial-knee-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T18:13:15.660Z</t>
+    <t>2026-07-18T19:22:30.027Z</t>
   </si>
   <si>
     <t>What Happens During Partial Knee Replacements | ReadyPatient</t>
@@ -2235,7 +2235,7 @@
     <t>knee/what-happens-during-total-knee-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T18:14:09.571Z</t>
+    <t>2026-07-18T19:23:24.262Z</t>
   </si>
   <si>
     <t>What Happens During Total Knee Replacements | ReadyPatient</t>
@@ -2250,7 +2250,7 @@
     <t>knee/what-is-a-clinical-study</t>
   </si>
   <si>
-    <t>2026-07-18T18:16:25.343Z</t>
+    <t>2026-07-18T19:25:48.328Z</t>
   </si>
   <si>
     <t>What is a clinical study?</t>
@@ -2265,7 +2265,7 @@
     <t>knee/what-is-insurance-prior-authorization</t>
   </si>
   <si>
-    <t>2026-07-18T18:17:05.190Z</t>
+    <t>2026-07-18T19:26:29.475Z</t>
   </si>
   <si>
     <t>What is Insurance Prior Authorization?</t>
@@ -2280,7 +2280,7 @@
     <t>knee/what-should-i-wear-to-the-hospital-for-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:00:01.270Z</t>
+    <t>2026-07-18T19:10:09.404Z</t>
   </si>
   <si>
     <t>What to Wear to the Hospital (and Pack) for Surgery | ReadyPatient</t>
@@ -2295,7 +2295,7 @@
     <t>knee/what-should-you-not-do-before-anesthesia</t>
   </si>
   <si>
-    <t>2026-07-18T18:01:14.959Z</t>
+    <t>2026-07-18T19:11:20.750Z</t>
   </si>
   <si>
     <t>Preparing for Anesthesia | ReadyPatient</t>
@@ -2310,7 +2310,7 @@
     <t>knee/what-to-expect-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:04:04.695Z</t>
+    <t>2026-07-18T19:14:05.062Z</t>
   </si>
   <si>
     <t>What to Expect After Joint Replacement Surgery</t>
@@ -2325,7 +2325,7 @@
     <t>knee/what-to-expect-at-your-first-orthopedic-visit</t>
   </si>
   <si>
-    <t>2026-07-18T18:18:51.714Z</t>
+    <t>2026-07-18T19:28:18.094Z</t>
   </si>
   <si>
     <t>What to Expect at Your First Orthopedic Visit | ReadyPatient</t>
@@ -2340,7 +2340,7 @@
     <t>knee/what-to-expect-during-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:17:41.464Z</t>
+    <t>2026-07-18T19:27:10.515Z</t>
   </si>
   <si>
     <t>What to Expect During Knee Replacement Surgery</t>
@@ -2355,7 +2355,7 @@
     <t>knee/whats-causing-my-knee-pain</t>
   </si>
   <si>
-    <t>2026-07-18T18:06:25.435Z</t>
+    <t>2026-07-18T19:16:10.381Z</t>
   </si>
   <si>
     <t>What’s Causing My Knee Pain?</t>
@@ -2370,7 +2370,7 @@
     <t>knee/whats-the-difference-between-a-general-practitioner-and-an-orthopedic-surgeon</t>
   </si>
   <si>
-    <t>2026-07-18T18:06:11.167Z</t>
+    <t>2026-07-18T19:15:57.767Z</t>
   </si>
   <si>
     <t>What's the Difference Between a General Practitioner and an Orthopedic Surgeon?</t>
@@ -2385,7 +2385,7 @@
     <t>knee/when-others-can-be-active-and-you-cant</t>
   </si>
   <si>
-    <t>2026-07-18T17:54:48.763Z</t>
+    <t>2026-07-18T19:05:00.781Z</t>
   </si>
   <si>
     <t>When Others Can Be Active and You Can’t</t>
@@ -2400,7 +2400,7 @@
     <t>knee/when-to-discuss-knee-pain-with-your-doctor</t>
   </si>
   <si>
-    <t>2026-07-18T18:02:33.571Z</t>
+    <t>2026-07-18T19:12:39.107Z</t>
   </si>
   <si>
     <t>When to Discuss Knee Pain with Your Doctor</t>
@@ -2415,7 +2415,7 @@
     <t>knee/why-is-everyone-calling-my-surgery-elective</t>
   </si>
   <si>
-    <t>2026-07-18T17:59:23.931Z</t>
+    <t>2026-07-18T19:09:32.255Z</t>
   </si>
   <si>
     <t>Why is Everyone Calling My Surgery Elective?</t>
@@ -2430,7 +2430,7 @@
     <t>knee/youve-been-referred-again</t>
   </si>
   <si>
-    <t>2026-07-18T17:53:22.319Z</t>
+    <t>2026-07-18T19:03:34.222Z</t>
   </si>
   <si>
     <t>You’ve Been Referred… Again</t>

--- a/tools/importer/reports/import-knee-article.report.xlsx
+++ b/tools/importer/reports/import-knee-article.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="807">
   <si>
     <t>_reportFile</t>
   </si>
@@ -46,7 +46,7 @@
     <t>knee/10-reasons-to-call-your-doctor-after-joint-replacement-surgery.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t/>
@@ -61,7 +61,7 @@
     <t>knee-article</t>
   </si>
   <si>
-    <t>2026-07-18T19:17:52.641Z</t>
+    <t>2026-07-19T06:25:53.464Z</t>
   </si>
   <si>
     <t>10 Reasons to Call Your Doctor After Joint Replacement Surgery</t>
@@ -76,7 +76,7 @@
     <t>knee/30-items-to-pack-for-a-hospital-stay-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:18:05.375Z</t>
+    <t>2026-07-19T06:26:13.206Z</t>
   </si>
   <si>
     <t>30 Items to Pack for a Hospital Stay After Joint Replacement Surgery</t>
@@ -94,7 +94,7 @@
     <t>knee/4-common-joint-replacement-questions-and-answers</t>
   </si>
   <si>
-    <t>2026-07-18T18:59:42.275Z</t>
+    <t>2026-07-19T06:04:23.747Z</t>
   </si>
   <si>
     <t>4 Common Joint Replacement Questions &amp; Answers</t>
@@ -109,7 +109,7 @@
     <t>knee/4-reasons-why-people-participate-in-a-clinical-study</t>
   </si>
   <si>
-    <t>2026-07-18T19:26:01.995Z</t>
+    <t>2026-07-19T06:33:34.733Z</t>
   </si>
   <si>
     <t>4 Reasons why People Participate in a Clinical Study</t>
@@ -124,7 +124,7 @@
     <t>knee/5-ideas-to-keep-your-marriage-strong-while-managing-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:18:53.744Z</t>
+    <t>2026-07-19T06:27:03.358Z</t>
   </si>
   <si>
     <t>5 Ideas to Keep Your Marriage Strong While Managing Pain</t>
@@ -136,13 +136,13 @@
     <t>knee/5-signs-its-time-to-talk-to-your-doctor-about-joint-replacement-surgery.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/5-signs-its-time-to-talk-to-your-doctor-about-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:29:47.889Z</t>
+    <t>2026-07-19T06:36:52.927Z</t>
   </si>
   <si>
     <t>5 Signs It’s Time to Talk to Your Doctor About Joint Replacement Surgery</t>
@@ -157,7 +157,7 @@
     <t>knee/5-ways-to-improve-sleep-when-you-have-chronic-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:07:44.862Z</t>
+    <t>2026-07-19T06:12:08.974Z</t>
   </si>
   <si>
     <t>Sleep Well With Chronic Pain | 5 Ways to Improve Sleep | ReadyPatient</t>
@@ -172,7 +172,7 @@
     <t>knee/6-different-items-to-pack-for-an-overnight-hospital-stay</t>
   </si>
   <si>
-    <t>2026-07-18T19:19:52.680Z</t>
+    <t>2026-07-19T06:28:04.662Z</t>
   </si>
   <si>
     <t>6 Different Items to Pack for an Overnight Hospital Stay</t>
@@ -184,13 +184,13 @@
     <t>knee/6-things-you-may-not-know-about-osteoarthritis.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/6-things-you-may-not-know-about-osteoarthritis</t>
   </si>
   <si>
-    <t>2026-07-18T19:13:40.240Z</t>
+    <t>2026-07-19T06:21:58.726Z</t>
   </si>
   <si>
     <t>6 Things You May Not Know About Osteoarthritis</t>
@@ -205,7 +205,7 @@
     <t>knee/6-ways-to-survive-the-holidays-with-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:17:22.908Z</t>
+    <t>2026-07-19T06:25:29.810Z</t>
   </si>
   <si>
     <t>6 Ways to Survive the Holidays with Joint Pain</t>
@@ -220,7 +220,7 @@
     <t>knee/7-things-to-look-for-in-a-remote-care-app</t>
   </si>
   <si>
-    <t>2026-07-18T19:08:58.199Z</t>
+    <t>2026-07-19T06:13:30.722Z</t>
   </si>
   <si>
     <t>7 Things to Look for in a Remote Care App</t>
@@ -235,7 +235,7 @@
     <t>knee/8-ways-to-stay-active-this-winter-with-arthritis</t>
   </si>
   <si>
-    <t>2026-07-18T19:19:29.208Z</t>
+    <t>2026-07-19T06:27:39.896Z</t>
   </si>
   <si>
     <t>8 Ways to Stay Active This Winter With Arthritis</t>
@@ -250,7 +250,7 @@
     <t>knee/9-fast-facts-about-arthritis</t>
   </si>
   <si>
-    <t>2026-07-18T19:07:58.532Z</t>
+    <t>2026-07-19T06:12:22.480Z</t>
   </si>
   <si>
     <t>9 Fast Facts About Arthritis</t>
@@ -262,13 +262,13 @@
     <t>knee/arthritic-painful-joints-motion-is-your-friend.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-figure","cards-figure","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-figure","cards-figure","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/arthritic-painful-joints-motion-is-your-friend</t>
   </si>
   <si>
-    <t>2026-07-18T19:03:19.822Z</t>
+    <t>2026-07-19T06:07:47.857Z</t>
   </si>
   <si>
     <t>Arthritic, Painful Joints: Motion Is Your Friend</t>
@@ -280,13 +280,13 @@
     <t>knee/arthritis-age-is-there-an-appropriate-age-for-arthritic-pain.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/arthritis-age-is-there-an-appropriate-age-for-arthritic-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:00:35.675Z</t>
+    <t>2026-07-19T06:05:11.771Z</t>
   </si>
   <si>
     <t>Arthritis Age - Is There an Appropriate Age for Arthritic Pain?</t>
@@ -298,13 +298,13 @@
     <t>knee/arthritis-can-you-tell-the-facts-from-the-myths.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/arthritis-can-you-tell-the-facts-from-the-myths</t>
   </si>
   <si>
-    <t>2026-07-18T19:17:10.202Z</t>
+    <t>2026-07-19T06:25:17.913Z</t>
   </si>
   <si>
     <t>Arthritis – Can You Tell the Facts From the Myths?</t>
@@ -319,7 +319,7 @@
     <t>knee/attitude-and-outcome</t>
   </si>
   <si>
-    <t>2026-07-18T19:20:17.996Z</t>
+    <t>2026-07-19T06:28:29.902Z</t>
   </si>
   <si>
     <t>Attitude and Outcome</t>
@@ -334,7 +334,7 @@
     <t>knee/beckys-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T19:18:30.327Z</t>
+    <t>2026-07-19T06:26:38.782Z</t>
   </si>
   <si>
     <t>Becky's Patient Story – Knee Replacement</t>
@@ -349,7 +349,7 @@
     <t>knee/bills-bills-and-more-bills</t>
   </si>
   <si>
-    <t>2026-07-18T19:26:56.547Z</t>
+    <t>2026-07-19T06:34:22.087Z</t>
   </si>
   <si>
     <t>Bills, Bills… and More Bills!</t>
@@ -364,7 +364,7 @@
     <t>knee/bone-health-basics</t>
   </si>
   <si>
-    <t>2026-07-18T19:13:27.479Z</t>
+    <t>2026-07-19T06:21:46.915Z</t>
   </si>
   <si>
     <t>Bone Health Basics</t>
@@ -382,7 +382,7 @@
     <t>knee/brittani-simpson-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T19:03:57.107Z</t>
+    <t>2026-07-19T06:08:21.547Z</t>
   </si>
   <si>
     <t>Brittani Simpson Patient Story – Knee Replacement</t>
@@ -394,13 +394,13 @@
     <t>knee/building-strength-before-joint-replacement-surgery.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/building-strength-before-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:24:03.610Z</t>
+    <t>2026-07-19T06:31:51.863Z</t>
   </si>
   <si>
     <t>Building Strength Before Joint Replacement Surgery</t>
@@ -415,7 +415,7 @@
     <t>knee/can-i-go-without-narcotics-after-my-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:01:01.283Z</t>
+    <t>2026-07-19T06:05:33.658Z</t>
   </si>
   <si>
     <t>Can I Go Without Narcotics After My Surgery?</t>
@@ -430,7 +430,7 @@
     <t>knee/can-you-go-home-the-same-day-after-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:09:56.867Z</t>
+    <t>2026-07-19T06:14:33.236Z</t>
   </si>
   <si>
     <t>Can you go home the same day after knee replacement?</t>
@@ -445,7 +445,7 @@
     <t>knee/can-you-walk-right-after-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:07:10.615Z</t>
+    <t>2026-07-19T06:11:33.305Z</t>
   </si>
   <si>
     <t>Can You Walk Right After Knee Replacement Surgery?</t>
@@ -457,13 +457,13 @@
     <t>knee/caring-for-a-loved-one-after-surgery.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/caring-for-a-loved-one-after-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:30:29.477Z</t>
+    <t>2026-07-19T06:37:31.745Z</t>
   </si>
   <si>
     <t>Caring for a Loved One After Surgery</t>
@@ -478,7 +478,7 @@
     <t>knee/common-post-op-questions-and-answers</t>
   </si>
   <si>
-    <t>2026-07-18T19:30:02.729Z</t>
+    <t>2026-07-19T06:37:05.746Z</t>
   </si>
   <si>
     <t>Common Post-Op Questions and Answers</t>
@@ -493,7 +493,7 @@
     <t>knee/common-recovery-exercises-after-hip-and-knee-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T19:23:49.407Z</t>
+    <t>2026-07-19T06:31:39.017Z</t>
   </si>
   <si>
     <t>Common recovery exercises after hip and knee replacements</t>
@@ -505,13 +505,13 @@
     <t>knee/common-side-effects-after-joint-replacement-surgery.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","columns-figure","columns-figure","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","columns-figure","columns-figure","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/common-side-effects-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:28:47.045Z</t>
+    <t>2026-07-19T06:36:02.659Z</t>
   </si>
   <si>
     <t>Common Side Effects After Joint Replacement Surgery | ReadyPatient</t>
@@ -529,7 +529,7 @@
     <t>knee/connies-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T19:04:48.276Z</t>
+    <t>2026-07-19T06:09:09.286Z</t>
   </si>
   <si>
     <t>Connie's Patient Story - Double Knee Replacement</t>
@@ -544,7 +544,7 @@
     <t>knee/consecutive-knee-or-hip-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T19:10:55.304Z</t>
+    <t>2026-07-19T06:15:37.472Z</t>
   </si>
   <si>
     <t>Consecutive Knee or Hip Replacements</t>
@@ -559,7 +559,7 @@
     <t>knee/considering-joint-surgery-while-living-alone</t>
   </si>
   <si>
-    <t>2026-07-18T19:22:04.148Z</t>
+    <t>2026-07-19T06:30:05.717Z</t>
   </si>
   <si>
     <t>Considering Joint Surgery While Living Alone</t>
@@ -574,7 +574,7 @@
     <t>knee/considering-joint-surgery-while-raising-a-family</t>
   </si>
   <si>
-    <t>2026-07-18T19:26:42.251Z</t>
+    <t>2026-07-19T06:34:11.561Z</t>
   </si>
   <si>
     <t>Considering Joint Surgery While Raising a Family</t>
@@ -589,7 +589,7 @@
     <t>knee/covid-19-has-delayed-my-joint-surgery-but-i-still-hurt</t>
   </si>
   <si>
-    <t>2026-07-18T19:11:37.974Z</t>
+    <t>2026-07-19T06:20:01.048Z</t>
   </si>
   <si>
     <t>COVID-19 Has Delayed My Joint Surgery, but I Still Hurt…</t>
@@ -604,7 +604,7 @@
     <t>knee/decoding-insurance-coding</t>
   </si>
   <si>
-    <t>2026-07-18T19:25:06.523Z</t>
+    <t>2026-07-19T06:32:47.481Z</t>
   </si>
   <si>
     <t>Decoding Insurance Coding</t>
@@ -619,7 +619,7 @@
     <t>knee/defining-your-personal-success</t>
   </si>
   <si>
-    <t>2026-07-18T19:21:08.099Z</t>
+    <t>2026-07-19T06:29:19.083Z</t>
   </si>
   <si>
     <t>Defining Your Personal Success</t>
@@ -637,7 +637,7 @@
     <t>knee/denise-good-partial-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:59:54.178Z</t>
+    <t>2026-07-19T06:04:35.460Z</t>
   </si>
   <si>
     <t>Denise's Patient Story - Partial Knee Replacement</t>
@@ -649,13 +649,13 @@
     <t>knee/diagnostic-imaging-tools-used-to-evaluate-your-joint-pain.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","columns-figure","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","columns-figure","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/diagnostic-imaging-tools-used-to-evaluate-your-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:02:04.248Z</t>
+    <t>2026-07-19T06:06:32.810Z</t>
   </si>
   <si>
     <t>Diagnostic Imaging Tools Used to Evaluate Your Joint Pain</t>
@@ -670,7 +670,7 @@
     <t>knee/do-i-have-bowlegs-or-knock-knees</t>
   </si>
   <si>
-    <t>2026-07-18T19:19:40.265Z</t>
+    <t>2026-07-19T06:27:52.527Z</t>
   </si>
   <si>
     <t>Do I Have Bowlegs or Knock Knees?</t>
@@ -685,7 +685,7 @@
     <t>knee/do-i-really-need-physical-therapy-after-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:02:16.861Z</t>
+    <t>2026-07-19T06:06:46.594Z</t>
   </si>
   <si>
     <t>Do I Really Need Physical Therapy After Surgery (Or Sometimes Even Before)?</t>
@@ -700,7 +700,7 @@
     <t>knee/do-you-stay-overnight-after-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:11:50.364Z</t>
+    <t>2026-07-19T06:20:13.222Z</t>
   </si>
   <si>
     <t>Does Knee Replacement Surgery Require an Overnight Stay? | ReadyPatient</t>
@@ -715,7 +715,7 @@
     <t>knee/donalds-patient-story-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:20:55.550Z</t>
+    <t>2026-07-19T06:29:07.550Z</t>
   </si>
   <si>
     <t>Donald's Patient Story – Knee Replacement</t>
@@ -727,13 +727,13 @@
     <t>knee/exercises-for-knee-pain.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","cards-article","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","columns-figure","cards-article","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/exercises-for-knee-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:29:17.604Z</t>
+    <t>2026-07-19T06:36:27.715Z</t>
   </si>
   <si>
     <t>Exercises for Knee Pain | ReadyPatient</t>
@@ -748,7 +748,7 @@
     <t>knee/fatigue-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:29:01.479Z</t>
+    <t>2026-07-19T06:36:16.128Z</t>
   </si>
   <si>
     <t>Fatigue after Joint Replacement Surgery | ReadyPatient</t>
@@ -760,13 +760,13 @@
     <t>knee/financial-considerations-for-the-younger-joint-replacement-patient.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/financial-considerations-for-the-younger-joint-replacement-patient</t>
   </si>
   <si>
-    <t>2026-07-18T19:01:38.378Z</t>
+    <t>2026-07-19T06:06:08.955Z</t>
   </si>
   <si>
     <t>Financial Considerations for the Younger Joint Replacement Patient</t>
@@ -781,7 +781,7 @@
     <t>knee/financial-planning-for-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:15:46.141Z</t>
+    <t>2026-07-19T06:24:04.734Z</t>
   </si>
   <si>
     <t>Financial Planning for Joint Replacement Surgery</t>
@@ -796,7 +796,7 @@
     <t>knee/five-things-to-consider-when-selecting-an-orthopedic-surgeon</t>
   </si>
   <si>
-    <t>2026-07-18T19:30:43.278Z</t>
+    <t>2026-07-19T06:37:44.455Z</t>
   </si>
   <si>
     <t>5 Things to Consider When Choosing an Orthopedic Surgeon</t>
@@ -811,7 +811,7 @@
     <t>knee/flying-and-medical-implants-etiquette-for-going-through-security</t>
   </si>
   <si>
-    <t>2026-07-18T19:30:56.069Z</t>
+    <t>2026-07-19T06:37:56.724Z</t>
   </si>
   <si>
     <t>Flying with a Medical Implant or Prosthetic Device | ReadyPatient</t>
@@ -826,7 +826,7 @@
     <t>knee/gardening-with-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:21:21.879Z</t>
+    <t>2026-07-19T06:29:30.244Z</t>
   </si>
   <si>
     <t>Gardening with Joint Pain</t>
@@ -841,7 +841,7 @@
     <t>knee/garys-patient-story-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:25:19.475Z</t>
+    <t>2026-07-19T06:32:58.378Z</t>
   </si>
   <si>
     <t>Gary's Patient Story – Knee Replacement</t>
@@ -856,7 +856,7 @@
     <t>knee/getting-a-second-opinion</t>
   </si>
   <si>
-    <t>2026-07-18T19:24:24.340Z</t>
+    <t>2026-07-19T06:32:03.369Z</t>
   </si>
   <si>
     <t>Getting a Second Opinion</t>
@@ -871,7 +871,7 @@
     <t>knee/handling-insurance-appeals</t>
   </si>
   <si>
-    <t>2026-07-18T19:27:23.202Z</t>
+    <t>2026-07-19T06:34:48.604Z</t>
   </si>
   <si>
     <t>Handling Insurance Appeals</t>
@@ -886,7 +886,7 @@
     <t>knee/having-fun-this-summer-despite-your-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:21:35.987Z</t>
+    <t>2026-07-19T06:29:42.024Z</t>
   </si>
   <si>
     <t>Having Fun this Summer Despite Your Joint Pain</t>
@@ -898,13 +898,13 @@
     <t>knee/hip-and-knee-replacement-cementless-vs-cemented-implants.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","columns-figure","columns-figure","cards-figure","cards-figure","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","columns-figure","columns-figure","cards-figure","cards-figure","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/hip-and-knee-replacement-cementless-vs-cemented-implants</t>
   </si>
   <si>
-    <t>2026-07-18T19:03:06.706Z</t>
+    <t>2026-07-19T06:07:35.795Z</t>
   </si>
   <si>
     <t>Hip and Knee Replacement: Cementless vs Cemented Implants</t>
@@ -919,7 +919,7 @@
     <t>knee/how-do-i-take-care-of-my-new-joint-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:16:22.117Z</t>
+    <t>2026-07-19T06:24:28.074Z</t>
   </si>
   <si>
     <t>How Do I Take Care of My New Joint Replacement?</t>
@@ -934,7 +934,7 @@
     <t>knee/how-long-will-it-take-to-get-back-to-normal-after-joint-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:05:44.877Z</t>
+    <t>2026-07-19T06:10:06.892Z</t>
   </si>
   <si>
     <t>How Long Will It Take To Get Back to Normal After Joint Surgery?</t>
@@ -949,7 +949,7 @@
     <t>knee/how-tech-savvy-are-you</t>
   </si>
   <si>
-    <t>2026-07-18T19:27:37.442Z</t>
+    <t>2026-07-19T06:35:03.325Z</t>
   </si>
   <si>
     <t>How tech-savvy are you?</t>
@@ -964,7 +964,7 @@
     <t>knee/how-to-prepare-for-revision-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:20:30.391Z</t>
+    <t>2026-07-19T06:28:43.306Z</t>
   </si>
   <si>
     <t>How to Prepare for Revision Surgery</t>
@@ -979,7 +979,7 @@
     <t>knee/incision-care-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:19:17.019Z</t>
+    <t>2026-07-19T06:27:27.591Z</t>
   </si>
   <si>
     <t>Incision Care After Joint Replacement Surgery</t>
@@ -994,7 +994,7 @@
     <t>knee/infection-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:05:13.536Z</t>
+    <t>2026-07-19T06:09:35.311Z</t>
   </si>
   <si>
     <t>Infection After Joint Replacement Surgery</t>
@@ -1009,7 +1009,7 @@
     <t>knee/insurance-and-joint-replacement-your-guide-to-getting-started</t>
   </si>
   <si>
-    <t>2026-07-18T19:14:56.428Z</t>
+    <t>2026-07-19T06:23:14.043Z</t>
   </si>
   <si>
     <t>Insurance and Joint Replacement - Your Guide to Getting Started</t>
@@ -1024,7 +1024,7 @@
     <t>knee/insurance-related-questions-to-ask</t>
   </si>
   <si>
-    <t>2026-07-18T19:24:52.280Z</t>
+    <t>2026-07-19T06:32:35.149Z</t>
   </si>
   <si>
     <t>Insurance Related Questions to Ask</t>
@@ -1039,7 +1039,7 @@
     <t>knee/is-arthritis-a-normal-part-of-aging</t>
   </si>
   <si>
-    <t>2026-07-18T19:01:26.305Z</t>
+    <t>2026-07-19T06:05:56.653Z</t>
   </si>
   <si>
     <t>Is Arthritis a Normal Part of Aging?</t>
@@ -1054,7 +1054,7 @@
     <t>knee/jims-patient-story-double-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:29:31.317Z</t>
+    <t>2026-07-19T06:36:40.627Z</t>
   </si>
   <si>
     <t>Jim’s Patient Story – Double Knee Replacement | ReadyPatient</t>
@@ -1069,7 +1069,7 @@
     <t>knee/joint-replacement-during-covid-questions-to-ask-your-doctor</t>
   </si>
   <si>
-    <t>2026-07-18T19:09:44.482Z</t>
+    <t>2026-07-19T06:14:20.441Z</t>
   </si>
   <si>
     <t>Joint Replacement During the COVID-19 Pandemic - Questions to Ask Your Doctor</t>
@@ -1084,7 +1084,7 @@
     <t>knee/joint-replacement-myth-1-surgical-robots-perform-the-whole-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:01:51.315Z</t>
+    <t>2026-07-19T06:06:21.130Z</t>
   </si>
   <si>
     <t>Joint Replacement Myth #1: Surgical Robots Perform the Whole Surgery</t>
@@ -1099,7 +1099,7 @@
     <t>knee/joint-replacement-myth-2-partial-knee-replacement-leads-to-total</t>
   </si>
   <si>
-    <t>2026-07-18T18:59:28.705Z</t>
+    <t>2026-07-19T06:04:12.866Z</t>
   </si>
   <si>
     <t>Joint Replacement Myth #2: Partial Knee Replacement Leads to Total</t>
@@ -1114,7 +1114,7 @@
     <t>knee/joint-replacement-myth-3-about-knee-injections</t>
   </si>
   <si>
-    <t>2026-07-18T19:04:23.042Z</t>
+    <t>2026-07-19T06:08:45.243Z</t>
   </si>
   <si>
     <t>Joint Replacement Myth #3: About Knee Injections</t>
@@ -1129,7 +1129,7 @@
     <t>knee/joint-replacement-surgery-during-the-covid-19-pandemic</t>
   </si>
   <si>
-    <t>2026-07-18T19:04:35.853Z</t>
+    <t>2026-07-19T06:08:57.604Z</t>
   </si>
   <si>
     <t>Joint Replacement Surgery During the COVID-19 Pandemic</t>
@@ -1141,13 +1141,13 @@
     <t>knee/keloid-and-hypertrophic-scars.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","columns-figure","columns-figure","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","columns-figure","columns-figure","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/keloid-and-hypertrophic-scars</t>
   </si>
   <si>
-    <t>2026-07-18T19:00:47.491Z</t>
+    <t>2026-07-19T06:05:22.429Z</t>
   </si>
   <si>
     <t>Keloid and Hypertrophic Scars</t>
@@ -1159,13 +1159,13 @@
     <t>knee/knee-implant-size-and-shape-do-they-matter.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","columns-figure","columns-figure","cards-figure","cards-figure","cards-figure","cards-article","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","columns-figure","columns-figure","cards-figure","cards-figure","cards-figure","cards-article","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/knee-implant-size-and-shape-do-they-matter</t>
   </si>
   <si>
-    <t>2026-07-18T19:00:20.373Z</t>
+    <t>2026-07-19T06:05:00.129Z</t>
   </si>
   <si>
     <t>Knee Implant Size and Shape – Do They Matter?</t>
@@ -1210,13 +1210,13 @@
     <t>knee/knee-pain-explained.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","columns-figure","columns-figure","columns-figure","cards-figure","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","columns-figure","columns-figure","columns-figure","cards-figure","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/knee-pain-explained</t>
   </si>
   <si>
-    <t>2026-07-18T18:58:21.225Z</t>
+    <t>2026-07-19T06:02:48.510Z</t>
   </si>
   <si>
     <t>Knee Pain Explained</t>
@@ -1228,7 +1228,7 @@
     <t>knee/knee-pain-relief-nonsurgical-treatment-options</t>
   </si>
   <si>
-    <t>2026-07-18T19:15:20.171Z</t>
+    <t>2026-07-19T06:23:39.562Z</t>
   </si>
   <si>
     <t>Knee Pain Relief &amp; Treatment - Nonsurigcal Treatment Options | ReadyPatient</t>
@@ -1243,7 +1243,7 @@
     <t>knee/knee-pain-relief-surgical-treatment-options</t>
   </si>
   <si>
-    <t>2026-07-18T19:13:02.551Z</t>
+    <t>2026-07-19T06:21:23.670Z</t>
   </si>
   <si>
     <t>Knee Pain Relief &amp; Surgical Treatment Options | ReadyPatient</t>
@@ -1258,7 +1258,7 @@
     <t>knee/know-your-procedure-options-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:20:42.689Z</t>
+    <t>2026-07-19T06:28:56.367Z</t>
   </si>
   <si>
     <t>Know Your Procedure Options – Knee Replacement</t>
@@ -1273,7 +1273,7 @@
     <t>knee/limitations-of-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:22:17.678Z</t>
+    <t>2026-07-19T06:30:17.199Z</t>
   </si>
   <si>
     <t>Limitations of Knee Replacement Surgery | ReadyPatient</t>
@@ -1288,7 +1288,7 @@
     <t>knee/lost-your-job-and-insurance-because-of-covid-19-but-need-joint-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:09:21.182Z</t>
+    <t>2026-07-19T06:13:56.959Z</t>
   </si>
   <si>
     <t>Lost Your Job Because of COVID-19</t>
@@ -1303,7 +1303,7 @@
     <t>knee/maintaining-joint-health</t>
   </si>
   <si>
-    <t>2026-07-18T19:26:14.976Z</t>
+    <t>2026-07-19T06:33:45.978Z</t>
   </si>
   <si>
     <t>Maintaining Joint Health</t>
@@ -1318,7 +1318,7 @@
     <t>knee/managing-a-loved-ones-postsurgical-care-during-covid-19</t>
   </si>
   <si>
-    <t>2026-07-18T19:12:02.423Z</t>
+    <t>2026-07-19T06:20:25.361Z</t>
   </si>
   <si>
     <t>Managing a Loved One’s Postsurgical Care During COVID-19</t>
@@ -1333,7 +1333,7 @@
     <t>knee/managing-constipation-after-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:07:20.997Z</t>
+    <t>2026-07-19T06:11:45.125Z</t>
   </si>
   <si>
     <t>Managing Constipation After Surgery</t>
@@ -1348,7 +1348,7 @@
     <t>knee/managing-your-stress-while-caring-for-another</t>
   </si>
   <si>
-    <t>2026-07-18T19:13:52.533Z</t>
+    <t>2026-07-19T06:22:12.681Z</t>
   </si>
   <si>
     <t>Managing Your Stress While Caring for Another</t>
@@ -1363,7 +1363,7 @@
     <t>knee/medical-tourniquets</t>
   </si>
   <si>
-    <t>2026-07-18T19:28:31.490Z</t>
+    <t>2026-07-19T06:35:51.650Z</t>
   </si>
   <si>
     <t>Medical Tourniquets | Tourniquets used during surgery | ReadyPatient</t>
@@ -1378,7 +1378,7 @@
     <t>knee/metal-hypersensitivity-and-allergies</t>
   </si>
   <si>
-    <t>2026-07-18T19:02:41.795Z</t>
+    <t>2026-07-19T06:07:10.142Z</t>
   </si>
   <si>
     <t>Metal Hypersensitivity and Allergies</t>
@@ -1393,7 +1393,7 @@
     <t>knee/moving-with-morning-joint-stiffness</t>
   </si>
   <si>
-    <t>2026-07-18T19:14:31.430Z</t>
+    <t>2026-07-19T06:22:48.734Z</t>
   </si>
   <si>
     <t>Moving with Morning Joint Stiffness</t>
@@ -1408,7 +1408,7 @@
     <t>knee/nancy-lopez-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T19:24:39.973Z</t>
+    <t>2026-07-19T06:32:23.054Z</t>
   </si>
   <si>
     <t>Nancy Lopez Patient Story – Knee Replacement</t>
@@ -1423,7 +1423,7 @@
     <t>knee/nicotine-and-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:06:59.146Z</t>
+    <t>2026-07-19T06:11:19.948Z</t>
   </si>
   <si>
     <t>Nicotine and Surgery</t>
@@ -1438,7 +1438,7 @@
     <t>knee/no-food-or-drink-after-midnight</t>
   </si>
   <si>
-    <t>2026-07-18T19:06:46.391Z</t>
+    <t>2026-07-19T06:11:07.198Z</t>
   </si>
   <si>
     <t>No Food or Drink After Midnight?</t>
@@ -1453,7 +1453,7 @@
     <t>knee/on-bended-knee-peters-patient-story-video</t>
   </si>
   <si>
-    <t>2026-07-18T19:14:17.634Z</t>
+    <t>2026-07-19T06:22:35.871Z</t>
   </si>
   <si>
     <t>Peter's Patient Story – Partial Knee Replacement</t>
@@ -1465,13 +1465,13 @@
     <t>knee/orthopedic-implants-and-metal-sensitivity.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-figure","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-figure","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/orthopedic-implants-and-metal-sensitivity</t>
   </si>
   <si>
-    <t>2026-07-18T19:22:43.479Z</t>
+    <t>2026-07-19T06:30:42.130Z</t>
   </si>
   <si>
     <t>Orthopedic Implants and Metal Sensitivity | ReadyPatient</t>
@@ -1486,7 +1486,7 @@
     <t>knee/outpatient-joint-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:05:57.059Z</t>
+    <t>2026-07-19T06:10:18.994Z</t>
   </si>
   <si>
     <t>Outpatient Joint Replacement</t>
@@ -1521,7 +1521,7 @@
     <t>knee/pain-isnt-weakness</t>
   </si>
   <si>
-    <t>2026-07-18T19:00:06.539Z</t>
+    <t>2026-07-19T06:04:48.802Z</t>
   </si>
   <si>
     <t>Pain Isn't "Weakness"</t>
@@ -1536,7 +1536,7 @@
     <t>knee/patricks-patient-story-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:03:46.027Z</t>
+    <t>2026-07-19T06:08:09.725Z</t>
   </si>
   <si>
     <t>Patrick's Patient Story – Knee Replacement</t>
@@ -1551,7 +1551,7 @@
     <t>knee/physical-therapy-options-in-the-covid-era</t>
   </si>
   <si>
-    <t>2026-07-18T19:01:14.070Z</t>
+    <t>2026-07-19T06:05:45.262Z</t>
   </si>
   <si>
     <t>Physical Therapy Options in the COVID Era</t>
@@ -1566,7 +1566,7 @@
     <t>knee/post-op-pain-management-strategies-for-orthopedic-patients</t>
   </si>
   <si>
-    <t>2026-07-18T19:12:50.524Z</t>
+    <t>2026-07-19T06:21:10.838Z</t>
   </si>
   <si>
     <t>Post-Op Pain Management Strategies for Orthopedic Patients</t>
@@ -1581,7 +1581,7 @@
     <t>knee/pre-op-and-post-op-joint-replacement-appointments-are-they-necessary</t>
   </si>
   <si>
-    <t>2026-07-18T19:08:22.694Z</t>
+    <t>2026-07-19T06:12:50.677Z</t>
   </si>
   <si>
     <t>Pre-op and Post-op Joint Replacement Appointments – Are They Necessary?</t>
@@ -1596,7 +1596,7 @@
     <t>knee/prepare-for-hip-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:06:21.781Z</t>
+    <t>2026-07-19T06:10:42.963Z</t>
   </si>
   <si>
     <t>Prepare for Ankle, Hip, Knee Replacement or Foot Surgery</t>
@@ -1608,13 +1608,13 @@
     <t>knee/preparing-for-joint-replacement-surgery.report.json</t>
   </si>
   <si>
-    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","columns-author","cards-resource","cards-resource"]</t>
+    <t>["content-hero-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","cards-article","author-bio","cards-resource","cards-resource"]</t>
   </si>
   <si>
     <t>knee/preparing-for-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:15:32.328Z</t>
+    <t>2026-07-19T06:23:51.934Z</t>
   </si>
   <si>
     <t>Preparing for Joint Replacement Surgery</t>
@@ -1629,7 +1629,7 @@
     <t>knee/preparing-for-surgery-when-you-cant-have-visitors</t>
   </si>
   <si>
-    <t>2026-07-18T19:09:09.320Z</t>
+    <t>2026-07-19T06:13:43.784Z</t>
   </si>
   <si>
     <t>Preparing for Surgery When You Can’t Have Visitors</t>
@@ -1644,7 +1644,7 @@
     <t>knee/questions-to-ask-when-considering-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:16:33.192Z</t>
+    <t>2026-07-19T06:24:39.446Z</t>
   </si>
   <si>
     <t>Questions to Ask When Considering Knee Replacement Surgery</t>
@@ -1662,7 +1662,7 @@
     <t>knee/rachaels-knee-replacement-surgery-story</t>
   </si>
   <si>
-    <t>2026-07-18T19:28:05.343Z</t>
+    <t>2026-07-19T06:35:27.837Z</t>
   </si>
   <si>
     <t>Rachael’s Knee Replacement Surgery Story | ReadyPatient</t>
@@ -1677,7 +1677,7 @@
     <t>knee/rebeccas-patient-story</t>
   </si>
   <si>
-    <t>2026-07-18T19:02:54.494Z</t>
+    <t>2026-07-19T06:07:22.633Z</t>
   </si>
   <si>
     <t>Rebecca's Patient Story – Knee Replacement</t>
@@ -1692,7 +1692,7 @@
     <t>knee/recovering-from-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:17:35.540Z</t>
+    <t>2026-07-19T06:25:41.391Z</t>
   </si>
   <si>
     <t>Recovering from Joint Replacement Surgery</t>
@@ -1707,7 +1707,7 @@
     <t>knee/referred-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:21:49.773Z</t>
+    <t>2026-07-19T06:29:53.206Z</t>
   </si>
   <si>
     <t>Referred Pain</t>
@@ -1722,7 +1722,7 @@
     <t>knee/resources-for-caregivers-caring-for-someone-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:27:52.694Z</t>
+    <t>2026-07-19T06:35:15.949Z</t>
   </si>
   <si>
     <t>Resources for Caregivers: Caring for Someone After Joint Replacement Surgery</t>
@@ -1737,7 +1737,7 @@
     <t>knee/returning-home-after-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:15:08.286Z</t>
+    <t>2026-07-19T06:23:27.119Z</t>
   </si>
   <si>
     <t>Returning Home After Knee Replacement Surgery</t>
@@ -1752,7 +1752,7 @@
     <t>knee/returning-to-activity-after-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:13:13.916Z</t>
+    <t>2026-07-19T06:21:35.673Z</t>
   </si>
   <si>
     <t>Returning to Activity After Knee Replacement Surgery</t>
@@ -1767,7 +1767,7 @@
     <t>knee/returning-to-activity-after-total-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:22:56.774Z</t>
+    <t>2026-07-19T06:30:52.694Z</t>
   </si>
   <si>
     <t>Returning to Activity After Total Knee Replacement | ReadyPatient</t>
@@ -1782,7 +1782,7 @@
     <t>knee/revision-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:06:08.872Z</t>
+    <t>2026-07-19T06:10:31.176Z</t>
   </si>
   <si>
     <t>Revision Joint Replacement Surgery</t>
@@ -1797,7 +1797,7 @@
     <t>knee/roberts-patient-story-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T18:59:04.947Z</t>
+    <t>2026-07-19T06:03:49.228Z</t>
   </si>
   <si>
     <t>Robert's Patient Story – Knee Replacement</t>
@@ -1812,7 +1812,7 @@
     <t>knee/robots-doing-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:20:05.423Z</t>
+    <t>2026-07-19T06:28:17.278Z</t>
   </si>
   <si>
     <t>Robots Doing Surgery?</t>
@@ -1827,7 +1827,7 @@
     <t>knee/robots-used-in-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T18:59:17.164Z</t>
+    <t>2026-07-19T06:04:01.680Z</t>
   </si>
   <si>
     <t>Robots Used in Surgery</t>
@@ -1842,7 +1842,7 @@
     <t>knee/scheduling-your-surgery-after-the-covid-19-quarantine</t>
   </si>
   <si>
-    <t>2026-07-18T19:06:33.149Z</t>
+    <t>2026-07-19T06:10:54.428Z</t>
   </si>
   <si>
     <t>Scheduling Your Surgery After the COVID-19 Quarantine</t>
@@ -1857,7 +1857,7 @@
     <t>knee/self-quarantine-before-and-after-your-elective-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:11:07.812Z</t>
+    <t>2026-07-19T06:15:50.730Z</t>
   </si>
   <si>
     <t>Self-Quarantine Before (and After) Your Elective Surgery</t>
@@ -1872,7 +1872,7 @@
     <t>knee/setting-realistic-expectations-prior-to-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:14:43.994Z</t>
+    <t>2026-07-19T06:23:01.423Z</t>
   </si>
   <si>
     <t>Setting Realistic Expectations Prior to Joint Replacement Surgery</t>
@@ -1887,7 +1887,7 @@
     <t>knee/shots-and-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:18:41.792Z</t>
+    <t>2026-07-19T06:26:51.641Z</t>
   </si>
   <si>
     <t>Shots and Joint Pain</t>
@@ -1902,7 +1902,7 @@
     <t>knee/so-your-doctor-said-you-need-joint-replacement-surgery-whats-next</t>
   </si>
   <si>
-    <t>2026-07-18T19:19:04.707Z</t>
+    <t>2026-07-19T06:27:15.734Z</t>
   </si>
   <si>
     <t>So Your Doctor Said You Need Joint Replacement Surgery… What’s Next?</t>
@@ -1917,7 +1917,7 @@
     <t>knee/social-distancing-and-joint-pain-a-few-things-to-consider</t>
   </si>
   <si>
-    <t>2026-07-18T19:07:33.927Z</t>
+    <t>2026-07-19T06:11:56.205Z</t>
   </si>
   <si>
     <t>Social Distancing and Joint Pain – A Few Things to Consider</t>
@@ -1932,7 +1932,7 @@
     <t>knee/spring-cleaning-with-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:18:17.906Z</t>
+    <t>2026-07-19T06:26:25.796Z</t>
   </si>
   <si>
     <t>Spring Cleaning With Joint Pain</t>
@@ -1947,7 +1947,7 @@
     <t>knee/superfoods-for-joint-health</t>
   </si>
   <si>
-    <t>2026-07-18T19:16:44.793Z</t>
+    <t>2026-07-19T06:24:51.514Z</t>
   </si>
   <si>
     <t>Superfoods for Joint Health</t>
@@ -1962,7 +1962,7 @@
     <t>knee/surgery-during-covid-19-what-are-hospitals-doing-to-manage-my-safety</t>
   </si>
   <si>
-    <t>2026-07-18T19:08:10.204Z</t>
+    <t>2026-07-19T06:12:36.310Z</t>
   </si>
   <si>
     <t>Surgery During COVID-19: What are Hospitals Doing to Manage My Safety?</t>
@@ -1977,7 +1977,7 @@
     <t>knee/surgical-principles-and-goals-for-total-knee-replacement</t>
   </si>
   <si>
-    <t>2026-07-18T19:23:36.296Z</t>
+    <t>2026-07-19T06:31:26.596Z</t>
   </si>
   <si>
     <t>Surgical Principles and Goals for Total Knee Replacement | ReadyPatient</t>
@@ -1992,7 +1992,7 @@
     <t>knee/swimming-a-great-exercise-for-every-age-and-fitness-level</t>
   </si>
   <si>
-    <t>2026-07-18T19:12:26.385Z</t>
+    <t>2026-07-19T06:20:47.675Z</t>
   </si>
   <si>
     <t>Swimming: A Great Exercise for Every Age and Fitness Level</t>
@@ -2007,7 +2007,7 @@
     <t>knee/technology-and-the-telehealth-landscape</t>
   </si>
   <si>
-    <t>2026-07-18T19:10:32.516Z</t>
+    <t>2026-07-19T06:15:10.640Z</t>
   </si>
   <si>
     <t>Technology and the Telehealth Landscape</t>
@@ -2022,7 +2022,7 @@
     <t>knee/telehealth-and-remote-care-evolving-in-the-age-of-covid-19</t>
   </si>
   <si>
-    <t>2026-07-18T19:12:15.343Z</t>
+    <t>2026-07-19T06:20:36.017Z</t>
   </si>
   <si>
     <t>Telehealth and Remote Care - Evolving in the Age of COVID-19</t>
@@ -2037,7 +2037,7 @@
     <t>knee/the-basics-of-using-a-walking-aid</t>
   </si>
   <si>
-    <t>2026-07-18T19:02:29.811Z</t>
+    <t>2026-07-19T06:06:57.774Z</t>
   </si>
   <si>
     <t>The Basics of Using a Walking Aid</t>
@@ -2052,7 +2052,7 @@
     <t>knee/the-benefits-of-outpatient-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:08:46.866Z</t>
+    <t>2026-07-19T06:13:17.348Z</t>
   </si>
   <si>
     <t>The Benefits of Outpatient Joint Replacement Surgery</t>
@@ -2067,7 +2067,7 @@
     <t>knee/the-effect-of-excess-weight-on-your-joints</t>
   </si>
   <si>
-    <t>2026-07-18T19:31:11.519Z</t>
+    <t>2026-07-19T06:38:08.189Z</t>
   </si>
   <si>
     <t>The Effect of Excess Weight on Your Joints</t>
@@ -2082,7 +2082,7 @@
     <t>knee/the-effect-of-joint-pain-on-you-and-your-family</t>
   </si>
   <si>
-    <t>2026-07-18T19:25:34.089Z</t>
+    <t>2026-07-19T06:33:10.946Z</t>
   </si>
   <si>
     <t>The Effect of Joint Pain on You and Your Family</t>
@@ -2097,7 +2097,7 @@
     <t>knee/the-pain-paradox</t>
   </si>
   <si>
-    <t>2026-07-18T19:04:09.674Z</t>
+    <t>2026-07-19T06:08:32.579Z</t>
   </si>
   <si>
     <t>The Pain Paradox</t>
@@ -2112,7 +2112,7 @@
     <t>knee/the-relationship-between-joint-pain-and-food</t>
   </si>
   <si>
-    <t>2026-07-18T19:08:33.936Z</t>
+    <t>2026-07-19T06:13:03.075Z</t>
   </si>
   <si>
     <t>The Relationship Between Joint Pain and Food</t>
@@ -2127,7 +2127,7 @@
     <t>knee/the-return-of-elective-procedures-explained</t>
   </si>
   <si>
-    <t>2026-07-18T19:10:44.634Z</t>
+    <t>2026-07-19T06:15:24.212Z</t>
   </si>
   <si>
     <t>The Return of Elective Procedures Explained</t>
@@ -2142,7 +2142,7 @@
     <t>knee/things-to-do-during-an-overnight-hospital-stay</t>
   </si>
   <si>
-    <t>2026-07-18T19:10:21.465Z</t>
+    <t>2026-07-19T06:14:57.417Z</t>
   </si>
   <si>
     <t>Things to Do During an Overnight Hospital Stay</t>
@@ -2157,7 +2157,7 @@
     <t>knee/types-of-joint-injections</t>
   </si>
   <si>
-    <t>2026-07-18T19:05:32.683Z</t>
+    <t>2026-07-19T06:09:53.413Z</t>
   </si>
   <si>
     <t>Types of Joint Injections</t>
@@ -2172,7 +2172,7 @@
     <t>knee/understanding-your-loved-ones-joint-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:16:56.660Z</t>
+    <t>2026-07-19T06:25:05.479Z</t>
   </si>
   <si>
     <t>Understanding Your Loved One’s Joint Pain</t>
@@ -2187,7 +2187,7 @@
     <t>knee/what-are-the-risks-of-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:30:15.588Z</t>
+    <t>2026-07-19T06:37:18.987Z</t>
   </si>
   <si>
     <t>What Are the Risks of Knee Replacement Surgery?</t>
@@ -2202,7 +2202,7 @@
     <t>knee/what-happens-during-partial-knee-and-total-knee-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T19:23:10.852Z</t>
+    <t>2026-07-19T06:31:03.751Z</t>
   </si>
   <si>
     <t>What Happens During Partial Knee and Total Knee Replacements | ReadyPatient</t>
@@ -2220,7 +2220,7 @@
     <t>knee/what-happens-during-partial-knee-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T19:22:30.027Z</t>
+    <t>2026-07-19T06:30:30.358Z</t>
   </si>
   <si>
     <t>What Happens During Partial Knee Replacements | ReadyPatient</t>
@@ -2235,7 +2235,7 @@
     <t>knee/what-happens-during-total-knee-replacements</t>
   </si>
   <si>
-    <t>2026-07-18T19:23:24.262Z</t>
+    <t>2026-07-19T06:31:15.881Z</t>
   </si>
   <si>
     <t>What Happens During Total Knee Replacements | ReadyPatient</t>
@@ -2250,7 +2250,7 @@
     <t>knee/what-is-a-clinical-study</t>
   </si>
   <si>
-    <t>2026-07-18T19:25:48.328Z</t>
+    <t>2026-07-19T06:33:22.649Z</t>
   </si>
   <si>
     <t>What is a clinical study?</t>
@@ -2265,7 +2265,7 @@
     <t>knee/what-is-insurance-prior-authorization</t>
   </si>
   <si>
-    <t>2026-07-18T19:26:29.475Z</t>
+    <t>2026-07-19T06:33:58.482Z</t>
   </si>
   <si>
     <t>What is Insurance Prior Authorization?</t>
@@ -2280,7 +2280,7 @@
     <t>knee/what-should-i-wear-to-the-hospital-for-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:10:09.404Z</t>
+    <t>2026-07-19T06:14:45.628Z</t>
   </si>
   <si>
     <t>What to Wear to the Hospital (and Pack) for Surgery | ReadyPatient</t>
@@ -2295,7 +2295,7 @@
     <t>knee/what-should-you-not-do-before-anesthesia</t>
   </si>
   <si>
-    <t>2026-07-18T19:11:20.750Z</t>
+    <t>2026-07-19T06:16:03.523Z</t>
   </si>
   <si>
     <t>Preparing for Anesthesia | ReadyPatient</t>
@@ -2310,7 +2310,7 @@
     <t>knee/what-to-expect-after-joint-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:14:05.062Z</t>
+    <t>2026-07-19T06:22:24.195Z</t>
   </si>
   <si>
     <t>What to Expect After Joint Replacement Surgery</t>
@@ -2325,7 +2325,7 @@
     <t>knee/what-to-expect-at-your-first-orthopedic-visit</t>
   </si>
   <si>
-    <t>2026-07-18T19:28:18.094Z</t>
+    <t>2026-07-19T06:35:38.658Z</t>
   </si>
   <si>
     <t>What to Expect at Your First Orthopedic Visit | ReadyPatient</t>
@@ -2340,7 +2340,7 @@
     <t>knee/what-to-expect-during-knee-replacement-surgery</t>
   </si>
   <si>
-    <t>2026-07-18T19:27:10.515Z</t>
+    <t>2026-07-19T06:34:34.681Z</t>
   </si>
   <si>
     <t>What to Expect During Knee Replacement Surgery</t>
@@ -2349,28 +2349,37 @@
     <t>https://www.thereadypatient.com/knee/what-to-expect-during-knee-replacement-surgery.html</t>
   </si>
   <si>
+    <t>knee/whats-causing-my-knee-pain.html.report.json</t>
+  </si>
+  <si>
+    <t>knee/whats-causing-my-knee-pain.html</t>
+  </si>
+  <si>
+    <t>2026-07-19T05:56:58.050Z</t>
+  </si>
+  <si>
+    <t>https://www.thereadypatient.com/knee/whats-causing-my-knee-pain.html</t>
+  </si>
+  <si>
     <t>knee/whats-causing-my-knee-pain.report.json</t>
   </si>
   <si>
     <t>knee/whats-causing-my-knee-pain</t>
   </si>
   <si>
-    <t>2026-07-18T19:16:10.381Z</t>
+    <t>2026-07-19T06:02:36.249Z</t>
   </si>
   <si>
     <t>What’s Causing My Knee Pain?</t>
   </si>
   <si>
-    <t>https://www.thereadypatient.com/knee/whats-causing-my-knee-pain.html</t>
-  </si>
-  <si>
     <t>knee/whats-the-difference-between-a-general-practitioner-and-an-orthopedic-surgeon.report.json</t>
   </si>
   <si>
     <t>knee/whats-the-difference-between-a-general-practitioner-and-an-orthopedic-surgeon</t>
   </si>
   <si>
-    <t>2026-07-18T19:15:57.767Z</t>
+    <t>2026-07-19T06:24:15.987Z</t>
   </si>
   <si>
     <t>What's the Difference Between a General Practitioner and an Orthopedic Surgeon?</t>
@@ -2385,7 +2394,7 @@
     <t>knee/when-others-can-be-active-and-you-cant</t>
   </si>
   <si>
-    <t>2026-07-18T19:05:00.781Z</t>
+    <t>2026-07-19T06:09:23.754Z</t>
   </si>
   <si>
     <t>When Others Can Be Active and You Can’t</t>
@@ -2400,7 +2409,7 @@
     <t>knee/when-to-discuss-knee-pain-with-your-doctor</t>
   </si>
   <si>
-    <t>2026-07-18T19:12:39.107Z</t>
+    <t>2026-07-19T06:20:58.976Z</t>
   </si>
   <si>
     <t>When to Discuss Knee Pain with Your Doctor</t>
@@ -2415,7 +2424,7 @@
     <t>knee/why-is-everyone-calling-my-surgery-elective</t>
   </si>
   <si>
-    <t>2026-07-18T19:09:32.255Z</t>
+    <t>2026-07-19T06:14:08.540Z</t>
   </si>
   <si>
     <t>Why is Everyone Calling My Surgery Elective?</t>
@@ -2430,7 +2439,7 @@
     <t>knee/youve-been-referred-again</t>
   </si>
   <si>
-    <t>2026-07-18T19:03:34.222Z</t>
+    <t>2026-07-19T06:07:59.161Z</t>
   </si>
   <si>
     <t>You’ve Been Referred… Again</t>
@@ -2825,7 +2834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -7575,36 +7584,36 @@
         <v>774</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C149" t="s">
-        <v>12</v>
+        <v>388</v>
       </c>
       <c r="D149" t="s">
-        <v>12</v>
+        <v>389</v>
       </c>
       <c r="E149" t="s">
         <v>775</v>
       </c>
       <c r="F149" t="s">
-        <v>14</v>
+        <v>391</v>
       </c>
       <c r="G149" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H149" t="s">
         <v>776</v>
       </c>
       <c r="I149" t="s">
+        <v>12</v>
+      </c>
+      <c r="J149" t="s">
         <v>777</v>
-      </c>
-      <c r="J149" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B150" t="s">
         <v>11</v>
@@ -7616,150 +7625,182 @@
         <v>12</v>
       </c>
       <c r="E150" t="s">
+        <v>779</v>
+      </c>
+      <c r="F150" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" t="s">
         <v>780</v>
       </c>
-      <c r="F150" t="s">
-        <v>14</v>
-      </c>
-      <c r="G150" t="s">
-        <v>15</v>
-      </c>
-      <c r="H150" t="s">
+      <c r="I150" t="s">
         <v>781</v>
       </c>
-      <c r="I150" t="s">
-        <v>782</v>
-      </c>
       <c r="J150" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>782</v>
+      </c>
+      <c r="B151" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" t="s">
+        <v>12</v>
+      </c>
+      <c r="E151" t="s">
+        <v>783</v>
+      </c>
+      <c r="F151" t="s">
+        <v>14</v>
+      </c>
+      <c r="G151" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" t="s">
         <v>784</v>
       </c>
-      <c r="B151" t="s">
-        <v>148</v>
-      </c>
-      <c r="C151" t="s">
-        <v>12</v>
-      </c>
-      <c r="D151" t="s">
-        <v>12</v>
-      </c>
-      <c r="E151" t="s">
+      <c r="I151" t="s">
         <v>785</v>
       </c>
-      <c r="F151" t="s">
-        <v>14</v>
-      </c>
-      <c r="G151" t="s">
-        <v>15</v>
-      </c>
-      <c r="H151" t="s">
+      <c r="J151" t="s">
         <v>786</v>
-      </c>
-      <c r="I151" t="s">
-        <v>787</v>
-      </c>
-      <c r="J151" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>787</v>
+      </c>
+      <c r="B152" t="s">
+        <v>148</v>
+      </c>
+      <c r="C152" t="s">
+        <v>12</v>
+      </c>
+      <c r="D152" t="s">
+        <v>12</v>
+      </c>
+      <c r="E152" t="s">
+        <v>788</v>
+      </c>
+      <c r="F152" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" t="s">
         <v>789</v>
       </c>
-      <c r="B152" t="s">
-        <v>11</v>
-      </c>
-      <c r="C152" t="s">
-        <v>12</v>
-      </c>
-      <c r="D152" t="s">
-        <v>12</v>
-      </c>
-      <c r="E152" t="s">
+      <c r="I152" t="s">
         <v>790</v>
       </c>
-      <c r="F152" t="s">
-        <v>14</v>
-      </c>
-      <c r="G152" t="s">
-        <v>15</v>
-      </c>
-      <c r="H152" t="s">
+      <c r="J152" t="s">
         <v>791</v>
-      </c>
-      <c r="I152" t="s">
-        <v>792</v>
-      </c>
-      <c r="J152" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>792</v>
+      </c>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" t="s">
+        <v>12</v>
+      </c>
+      <c r="E153" t="s">
+        <v>793</v>
+      </c>
+      <c r="F153" t="s">
+        <v>14</v>
+      </c>
+      <c r="G153" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" t="s">
         <v>794</v>
       </c>
-      <c r="B153" t="s">
-        <v>41</v>
-      </c>
-      <c r="C153" t="s">
-        <v>12</v>
-      </c>
-      <c r="D153" t="s">
-        <v>12</v>
-      </c>
-      <c r="E153" t="s">
+      <c r="I153" t="s">
         <v>795</v>
       </c>
-      <c r="F153" t="s">
-        <v>14</v>
-      </c>
-      <c r="G153" t="s">
-        <v>15</v>
-      </c>
-      <c r="H153" t="s">
+      <c r="J153" t="s">
         <v>796</v>
-      </c>
-      <c r="I153" t="s">
-        <v>797</v>
-      </c>
-      <c r="J153" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>797</v>
+      </c>
+      <c r="B154" t="s">
+        <v>41</v>
+      </c>
+      <c r="C154" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" t="s">
+        <v>12</v>
+      </c>
+      <c r="E154" t="s">
+        <v>798</v>
+      </c>
+      <c r="F154" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" t="s">
         <v>799</v>
       </c>
-      <c r="B154" t="s">
+      <c r="I154" t="s">
+        <v>800</v>
+      </c>
+      <c r="J154" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>802</v>
+      </c>
+      <c r="B155" t="s">
         <v>127</v>
       </c>
-      <c r="C154" t="s">
-        <v>12</v>
-      </c>
-      <c r="D154" t="s">
-        <v>12</v>
-      </c>
-      <c r="E154" t="s">
-        <v>800</v>
-      </c>
-      <c r="F154" t="s">
-        <v>14</v>
-      </c>
-      <c r="G154" t="s">
-        <v>15</v>
-      </c>
-      <c r="H154" t="s">
-        <v>801</v>
-      </c>
-      <c r="I154" t="s">
-        <v>802</v>
-      </c>
-      <c r="J154" t="s">
+      <c r="C155" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" t="s">
+        <v>12</v>
+      </c>
+      <c r="E155" t="s">
         <v>803</v>
+      </c>
+      <c r="F155" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" t="s">
+        <v>804</v>
+      </c>
+      <c r="I155" t="s">
+        <v>805</v>
+      </c>
+      <c r="J155" t="s">
+        <v>806</v>
       </c>
     </row>
   </sheetData>
